--- a/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
@@ -946,12 +946,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Compose_1200'!$A$13:$A$59</f>
+              <f>'Compose_1200'!$A$13:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Compose_1200'!$J$13:$J$59</f>
+              <f>'Compose_1200'!$J$13:$J$64</f>
             </numRef>
           </val>
         </ser>
@@ -978,12 +978,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Compose_1200'!$A$13:$A$59</f>
+              <f>'Compose_1200'!$A$13:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Compose_1200'!$H$13:$H$59</f>
+              <f>'Compose_1200'!$H$13:$H$64</f>
             </numRef>
           </val>
         </ser>
@@ -1010,12 +1010,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Compose_1200'!$A$13:$A$59</f>
+              <f>'Compose_1200'!$A$13:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Compose_1200'!$I$13:$I$59</f>
+              <f>'Compose_1200'!$I$13:$I$64</f>
             </numRef>
           </val>
         </ser>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="B38" s="14">
-        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table — etendre leve",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — etendre leve)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B44" s="14">
-        <f>IF(B42&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B42&gt;=Stage_Storage!E18,"Hors table — etendre leve",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1))+(B42-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <f>IF(B42&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B42&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — etendre leve)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1))+(B42-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B42,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Remplacez les aires par votre nouveau leve (plus d'aire attendue sans emprise Ø900). 37.28 m = ancienne limite patron.</t>
+          <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Remplacez les aires par votre nouveau leve (plus d'aire attendue sans emprise Ø900). Surfaces jaunes synchronisees avec votre copie locale (sept. 2026). 37.28 m = cote cle / limite patron.</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
     </row>
     <row r="13">
       <c r="A13" s="28" t="n">
-        <v>36</v>
+        <v>36.01</v>
       </c>
       <c r="B13" s="10" t="n">
-        <v>280</v>
+        <v>419</v>
       </c>
       <c r="C13" s="28">
         <f>A13-A12</f>
@@ -5106,7 +5106,7 @@
         <v>37.28</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>850</v>
+        <v>2198</v>
       </c>
       <c r="C16" s="31">
         <f>A16-A15</f>
@@ -5122,16 +5122,16 @@
       </c>
       <c r="F16" s="33" t="inlineStr">
         <is>
-          <t>Limite patron (ex) — a recalibrer</t>
+          <t>Limite patron / cote cle</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="28" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="B17" s="10" t="n">
-        <v>1100</v>
+        <v>1516</v>
       </c>
       <c r="C17" s="28">
         <f>A17-A16</f>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="18">
       <c r="A18" s="28" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="B18" s="10" t="n">
-        <v>2800</v>
+        <v>3746</v>
       </c>
       <c r="C18" s="28">
         <f>A18-A17</f>
@@ -5232,7 +5232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7302,6 +7302,211 @@
       </c>
       <c r="J59" s="9">
         <f>H59+I59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="B60" s="28">
+        <f>A60-$B$10</f>
+        <v/>
+      </c>
+      <c r="C60" s="28">
+        <f>MAX(0,A60-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D60" s="19">
+        <f>IF(C60&lt;=0,0,($B$5+$B$7*C60)*C60)</f>
+        <v/>
+      </c>
+      <c r="E60" s="18">
+        <f>D60*$B$9</f>
+        <v/>
+      </c>
+      <c r="F60" s="18">
+        <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G60" s="24">
+        <f>E60+F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="19">
+        <f>IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))</f>
+        <v/>
+      </c>
+      <c r="I60" s="19">
+        <f>IF(C60&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D60*IF(($B$5+2*C60*SQRT(1+$B$7^2))&lt;=0,0,((D60/($B$5+2*C60*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J60" s="9">
+        <f>H60+I60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="B61" s="28">
+        <f>A61-$B$10</f>
+        <v/>
+      </c>
+      <c r="C61" s="28">
+        <f>MAX(0,A61-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D61" s="19">
+        <f>IF(C61&lt;=0,0,($B$5+$B$7*C61)*C61)</f>
+        <v/>
+      </c>
+      <c r="E61" s="18">
+        <f>D61*$B$9</f>
+        <v/>
+      </c>
+      <c r="F61" s="18">
+        <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G61" s="24">
+        <f>E61+F61</f>
+        <v/>
+      </c>
+      <c r="H61" s="19">
+        <f>IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))</f>
+        <v/>
+      </c>
+      <c r="I61" s="19">
+        <f>IF(C61&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D61*IF(($B$5+2*C61*SQRT(1+$B$7^2))&lt;=0,0,((D61/($B$5+2*C61*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J61" s="9">
+        <f>H61+I61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="B62" s="28">
+        <f>A62-$B$10</f>
+        <v/>
+      </c>
+      <c r="C62" s="28">
+        <f>MAX(0,A62-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D62" s="19">
+        <f>IF(C62&lt;=0,0,($B$5+$B$7*C62)*C62)</f>
+        <v/>
+      </c>
+      <c r="E62" s="18">
+        <f>D62*$B$9</f>
+        <v/>
+      </c>
+      <c r="F62" s="18">
+        <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G62" s="24">
+        <f>E62+F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="19">
+        <f>IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))</f>
+        <v/>
+      </c>
+      <c r="I62" s="19">
+        <f>IF(C62&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D62*IF(($B$5+2*C62*SQRT(1+$B$7^2))&lt;=0,0,((D62/($B$5+2*C62*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J62" s="9">
+        <f>H62+I62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B63" s="28">
+        <f>A63-$B$10</f>
+        <v/>
+      </c>
+      <c r="C63" s="28">
+        <f>MAX(0,A63-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D63" s="19">
+        <f>IF(C63&lt;=0,0,($B$5+$B$7*C63)*C63)</f>
+        <v/>
+      </c>
+      <c r="E63" s="18">
+        <f>D63*$B$9</f>
+        <v/>
+      </c>
+      <c r="F63" s="18">
+        <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G63" s="24">
+        <f>E63+F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="19">
+        <f>IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))</f>
+        <v/>
+      </c>
+      <c r="I63" s="19">
+        <f>IF(C63&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D63*IF(($B$5+2*C63*SQRT(1+$B$7^2))&lt;=0,0,((D63/($B$5+2*C63*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J63" s="9">
+        <f>H63+I63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B64" s="28">
+        <f>A64-$B$10</f>
+        <v/>
+      </c>
+      <c r="C64" s="28">
+        <f>MAX(0,A64-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D64" s="19">
+        <f>IF(C64&lt;=0,0,($B$5+$B$7*C64)*C64)</f>
+        <v/>
+      </c>
+      <c r="E64" s="18">
+        <f>D64*$B$9</f>
+        <v/>
+      </c>
+      <c r="F64" s="18">
+        <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G64" s="24">
+        <f>E64+F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="19">
+        <f>IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))</f>
+        <v/>
+      </c>
+      <c r="I64" s="19">
+        <f>IF(C64&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D64*IF(($B$5+2*C64*SQRT(1+$B$7^2))&lt;=0,0,((D64/($B$5+2*C64*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J64" s="9">
+        <f>H64+I64</f>
         <v/>
       </c>
     </row>
@@ -7457,11 +7662,11 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>IF(F10&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F10&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F10,Compose_1200!$G$13:$G$59,1))+(F10-INDEX(Compose_1200!$G$13:$G$59,MATCH(F10,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F10,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F10,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F10,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F10,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F10&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F10&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F10,Compose_1200!$G$13:$G$64,1))+(F10-INDEX(Compose_1200!$G$13:$G$64,MATCH(F10,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F10,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F10,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F10,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F10,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D11" s="19">
-        <f>IF(F10&lt;=0.01,MIN(0.5*(B10+B11),$B$4),IF(C11&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C11&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C11,Compose_1200!$A$13:$A$59,1))+(C11-INDEX(Compose_1200!$A$13:$A$59,MATCH(C11,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C11,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C11,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C11,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C11,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F10&lt;=0.01,MIN(0.5*(B10+B11),$B$4),IF(C11&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C11&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C11,Compose_1200!$A$13:$A$64,1))+(C11-INDEX(Compose_1200!$A$13:$A$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C11,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E11" s="18">
@@ -7487,11 +7692,11 @@
         <v/>
       </c>
       <c r="C12" s="19">
-        <f>IF(F11&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F11&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F11,Compose_1200!$G$13:$G$59,1))+(F11-INDEX(Compose_1200!$G$13:$G$59,MATCH(F11,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F11,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F11,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F11,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F11,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F11&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F11&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F11,Compose_1200!$G$13:$G$64,1))+(F11-INDEX(Compose_1200!$G$13:$G$64,MATCH(F11,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F11,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F11,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F11,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F11,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D12" s="19">
-        <f>IF(F11&lt;=0.01,MIN(0.5*(B11+B12),$B$4),IF(C12&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C12&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C12,Compose_1200!$A$13:$A$59,1))+(C12-INDEX(Compose_1200!$A$13:$A$59,MATCH(C12,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C12,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C12,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C12,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C12,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F11&lt;=0.01,MIN(0.5*(B11+B12),$B$4),IF(C12&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C12&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C12,Compose_1200!$A$13:$A$64,1))+(C12-INDEX(Compose_1200!$A$13:$A$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C12,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E12" s="18">
@@ -7517,11 +7722,11 @@
         <v/>
       </c>
       <c r="C13" s="19">
-        <f>IF(F12&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F12&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F12,Compose_1200!$G$13:$G$59,1))+(F12-INDEX(Compose_1200!$G$13:$G$59,MATCH(F12,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F12,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F12,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F12,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F12,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F12&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F12&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F12,Compose_1200!$G$13:$G$64,1))+(F12-INDEX(Compose_1200!$G$13:$G$64,MATCH(F12,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F12,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F12,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F12,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F12,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D13" s="19">
-        <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$4),IF(C13&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C13&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C13,Compose_1200!$A$13:$A$59,1))+(C13-INDEX(Compose_1200!$A$13:$A$59,MATCH(C13,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C13,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C13,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C13,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C13,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$4),IF(C13&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C13&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C13,Compose_1200!$A$13:$A$64,1))+(C13-INDEX(Compose_1200!$A$13:$A$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C13,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E13" s="18">
@@ -7547,11 +7752,11 @@
         <v/>
       </c>
       <c r="C14" s="19">
-        <f>IF(F13&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F13&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F13,Compose_1200!$G$13:$G$59,1))+(F13-INDEX(Compose_1200!$G$13:$G$59,MATCH(F13,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F13,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F13,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F13,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F13,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F13&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F13&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F13,Compose_1200!$G$13:$G$64,1))+(F13-INDEX(Compose_1200!$G$13:$G$64,MATCH(F13,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F13,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F13,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F13,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F13,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D14" s="19">
-        <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$4),IF(C14&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C14&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C14,Compose_1200!$A$13:$A$59,1))+(C14-INDEX(Compose_1200!$A$13:$A$59,MATCH(C14,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C14,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C14,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C14,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C14,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$4),IF(C14&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C14&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C14,Compose_1200!$A$13:$A$64,1))+(C14-INDEX(Compose_1200!$A$13:$A$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C14,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E14" s="18">
@@ -7577,11 +7782,11 @@
         <v/>
       </c>
       <c r="C15" s="19">
-        <f>IF(F14&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F14&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F14,Compose_1200!$G$13:$G$59,1))+(F14-INDEX(Compose_1200!$G$13:$G$59,MATCH(F14,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F14,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F14,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F14,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F14,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F14&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F14&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F14,Compose_1200!$G$13:$G$64,1))+(F14-INDEX(Compose_1200!$G$13:$G$64,MATCH(F14,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F14,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F14,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F14,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F14,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D15" s="19">
-        <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$4),IF(C15&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C15&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C15,Compose_1200!$A$13:$A$59,1))+(C15-INDEX(Compose_1200!$A$13:$A$59,MATCH(C15,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C15,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C15,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C15,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C15,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$4),IF(C15&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C15&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C15,Compose_1200!$A$13:$A$64,1))+(C15-INDEX(Compose_1200!$A$13:$A$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C15,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -7607,11 +7812,11 @@
         <v/>
       </c>
       <c r="C16" s="19">
-        <f>IF(F15&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F15&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F15,Compose_1200!$G$13:$G$59,1))+(F15-INDEX(Compose_1200!$G$13:$G$59,MATCH(F15,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F15,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F15,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F15,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F15,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F15,Compose_1200!$G$13:$G$64,1))+(F15-INDEX(Compose_1200!$G$13:$G$64,MATCH(F15,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F15,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F15,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F15,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F15,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="19">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C16&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C16,Compose_1200!$A$13:$A$59,1))+(C16-INDEX(Compose_1200!$A$13:$A$59,MATCH(C16,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C16,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C16,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C16,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C16,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C16,Compose_1200!$A$13:$A$64,1))+(C16-INDEX(Compose_1200!$A$13:$A$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C16,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -7637,11 +7842,11 @@
         <v/>
       </c>
       <c r="C17" s="19">
-        <f>IF(F16&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F16&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F16,Compose_1200!$G$13:$G$59,1))+(F16-INDEX(Compose_1200!$G$13:$G$59,MATCH(F16,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F16,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F16,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F16,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F16,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F16,Compose_1200!$G$13:$G$64,1))+(F16-INDEX(Compose_1200!$G$13:$G$64,MATCH(F16,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F16,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F16,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F16,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F16,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="19">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C17&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C17,Compose_1200!$A$13:$A$59,1))+(C17-INDEX(Compose_1200!$A$13:$A$59,MATCH(C17,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C17,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C17,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C17,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C17,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C17,Compose_1200!$A$13:$A$64,1))+(C17-INDEX(Compose_1200!$A$13:$A$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C17,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -7667,11 +7872,11 @@
         <v/>
       </c>
       <c r="C18" s="19">
-        <f>IF(F17&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F17&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F17,Compose_1200!$G$13:$G$59,1))+(F17-INDEX(Compose_1200!$G$13:$G$59,MATCH(F17,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F17,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F17,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F17,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F17,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F17,Compose_1200!$G$13:$G$64,1))+(F17-INDEX(Compose_1200!$G$13:$G$64,MATCH(F17,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F17,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F17,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F17,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F17,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="19">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C18&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C18,Compose_1200!$A$13:$A$59,1))+(C18-INDEX(Compose_1200!$A$13:$A$59,MATCH(C18,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C18,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C18,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C18,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C18,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C18,Compose_1200!$A$13:$A$64,1))+(C18-INDEX(Compose_1200!$A$13:$A$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C18,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="18">
@@ -7697,11 +7902,11 @@
         <v/>
       </c>
       <c r="C19" s="19">
-        <f>IF(F18&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F18&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F18,Compose_1200!$G$13:$G$59,1))+(F18-INDEX(Compose_1200!$G$13:$G$59,MATCH(F18,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F18,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F18,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F18,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F18,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F18,Compose_1200!$G$13:$G$64,1))+(F18-INDEX(Compose_1200!$G$13:$G$64,MATCH(F18,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F18,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F18,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F18,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F18,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="19">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C19&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C19,Compose_1200!$A$13:$A$59,1))+(C19-INDEX(Compose_1200!$A$13:$A$59,MATCH(C19,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C19,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C19,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C19,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C19,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C19,Compose_1200!$A$13:$A$64,1))+(C19-INDEX(Compose_1200!$A$13:$A$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C19,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="18">
@@ -7727,11 +7932,11 @@
         <v/>
       </c>
       <c r="C20" s="19">
-        <f>IF(F19&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F19&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F19,Compose_1200!$G$13:$G$59,1))+(F19-INDEX(Compose_1200!$G$13:$G$59,MATCH(F19,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F19,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F19,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F19,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F19,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F19,Compose_1200!$G$13:$G$64,1))+(F19-INDEX(Compose_1200!$G$13:$G$64,MATCH(F19,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F19,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F19,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F19,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F19,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="19">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C20&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C20,Compose_1200!$A$13:$A$59,1))+(C20-INDEX(Compose_1200!$A$13:$A$59,MATCH(C20,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C20,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C20,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C20,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C20,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C20,Compose_1200!$A$13:$A$64,1))+(C20-INDEX(Compose_1200!$A$13:$A$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C20,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="18">
@@ -7757,11 +7962,11 @@
         <v/>
       </c>
       <c r="C21" s="19">
-        <f>IF(F20&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F20&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F20,Compose_1200!$G$13:$G$59,1))+(F20-INDEX(Compose_1200!$G$13:$G$59,MATCH(F20,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F20,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F20,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F20,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F20,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F20,Compose_1200!$G$13:$G$64,1))+(F20-INDEX(Compose_1200!$G$13:$G$64,MATCH(F20,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F20,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F20,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F20,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F20,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="19">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C21&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C21,Compose_1200!$A$13:$A$59,1))+(C21-INDEX(Compose_1200!$A$13:$A$59,MATCH(C21,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C21,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C21,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C21,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C21,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C21,Compose_1200!$A$13:$A$64,1))+(C21-INDEX(Compose_1200!$A$13:$A$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C21,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="18">
@@ -7787,11 +7992,11 @@
         <v/>
       </c>
       <c r="C22" s="19">
-        <f>IF(F21&lt;=INDEX(Compose_1200!$G$13:$G$59,1),INDEX(Compose_1200!$A$13:$A$59,1),IF(F21&gt;=INDEX(Compose_1200!$G$13:$G$59,ROWS(Compose_1200!$G$13:$G$59)),INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$A$13:$A$59,MATCH(F21,Compose_1200!$G$13:$G$59,1))+(F21-INDEX(Compose_1200!$G$13:$G$59,MATCH(F21,Compose_1200!$G$13:$G$59,1)))/(INDEX(Compose_1200!$G$13:$G$59,MATCH(F21,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$G$13:$G$59,MATCH(F21,Compose_1200!$G$13:$G$59,1)))*(INDEX(Compose_1200!$A$13:$A$59,MATCH(F21,Compose_1200!$G$13:$G$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(F21,Compose_1200!$G$13:$G$59,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_1200!$G$13:$G$64,1),INDEX(Compose_1200!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_1200!$G$13:$G$64,ROWS(Compose_1200!$G$13:$G$64)),INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$A$13:$A$64,MATCH(F21,Compose_1200!$G$13:$G$64,1))+(F21-INDEX(Compose_1200!$G$13:$G$64,MATCH(F21,Compose_1200!$G$13:$G$64,1)))/(INDEX(Compose_1200!$G$13:$G$64,MATCH(F21,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$G$13:$G$64,MATCH(F21,Compose_1200!$G$13:$G$64,1)))*(INDEX(Compose_1200!$A$13:$A$64,MATCH(F21,Compose_1200!$G$13:$G$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(F21,Compose_1200!$G$13:$G$64,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="19">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_1200!$A$13:$A$59,1),INDEX(Compose_1200!$J$13:$J$59,1),IF(C22&gt;=INDEX(Compose_1200!$A$13:$A$59,ROWS(Compose_1200!$A$13:$A$59)),INDEX(Compose_1200!$J$13:$J$59,ROWS(Compose_1200!$J$13:$J$59)),INDEX(Compose_1200!$J$13:$J$59,MATCH(C22,Compose_1200!$A$13:$A$59,1))+(C22-INDEX(Compose_1200!$A$13:$A$59,MATCH(C22,Compose_1200!$A$13:$A$59,1)))/(INDEX(Compose_1200!$A$13:$A$59,MATCH(C22,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$A$13:$A$59,MATCH(C22,Compose_1200!$A$13:$A$59,1)))*(INDEX(Compose_1200!$J$13:$J$59,MATCH(C22,Compose_1200!$A$13:$A$59,1)+1)-INDEX(Compose_1200!$J$13:$J$59,MATCH(C22,Compose_1200!$A$13:$A$59,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C22,Compose_1200!$A$13:$A$64,1))+(C22-INDEX(Compose_1200!$A$13:$A$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C22,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="18">

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
@@ -4942,7 +4942,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Remplacez les aires par votre nouveau leve (plus d'aire attendue sans emprise Ø900). Surfaces jaunes synchronisees avec votre copie locale (sept. 2026). 37.28 m = cote cle / limite patron.</t>
+          <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Remplacez les aires par votre nouveau leve (plus d'aire attendue sans emprise Ø900). Surfaces jaunes synchronisees avec votre copie locale. Ligne 37.28 m: Role laisse vide (comme votre fichier local).</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,7 @@
         <f>E15+D16</f>
         <v/>
       </c>
-      <c r="F16" s="33" t="inlineStr">
-        <is>
-          <t>Limite patron / cote cle</t>
-        </is>
-      </c>
+      <c r="F16" s="33" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="28" t="n">

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
@@ -1682,7 +1682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1703,7 +1703,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hypotheses: le Ø900 est elimine; plus d'aire de retention. Entree = hydrogramme (Ø1500). Sortie = Ø1200. Option: fossé/berme au-dessus d'une cote crest. Cellules JAUNES = entrees.</t>
+          <t>Hypotheses: le Ø900 est elimine; un seul bassin (surfaces = Zone1+Zone2 du leve). Entree = hydrogramme (Ø1500). Sortie = Ø1200. Limite ville WSE = 37.40 m (B27). B25=0 → volume = leve seul (pas de V_ditch). Cellules JAUNES = entrees. Aluminium ondule: augmenter n (ex. 0.024) sur Courbe_QH_1200.</t>
         </is>
       </c>
     </row>
@@ -1745,6 +1745,11 @@
       <c r="B10" s="5" t="n">
         <v>0.013</v>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>beton ~0.013; aluminium ondule typ. 0.022–0.025 (changer aussi Courbe_QH_1200)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1890,11 +1895,26 @@
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>4000</v>
+        <v>2320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plus grande qu'avant (plus d'aire retention) — affiner avec le leve</t>
+          <t>Raccourci Methode B seulement (H=V/A). Ex. A@37.40≈2320 — PAS un 2e bassin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Inclure V_ditch trapeze? (1=oui, 0=leve seul)</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0 = recommande si Stage_Storage contient deja le fosse (V=leve seul; Q_overflow garde b,z,L). 1 = ajoute V_ditch = A_trapeze x L (risque double volume).</t>
         </is>
       </c>
     </row>
@@ -1912,11 +1932,11 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>37.28</v>
+        <v>37.4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Si WSE &lt; crest → Q_overflow = 0</t>
+          <t>Limite ville = 37.40 m par defaut. Si WSE &lt; crest → Q_overflow = 0</t>
         </is>
       </c>
     </row>
@@ -1986,10 +2006,9 @@
           <t>Q_1200(WSE) + Q_overflow(WSE)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>V = V_pond + V_ditch — Compose_1200 + Calcul_C</t>
-        </is>
+      <c r="C33">
+        <f>IF(B25=1,"V=V_pond+V_ditch","V=V_pond (leve seul, B25=0)") — Compose_1200 + Calcul_C</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2097,14 +2116,14 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Resultats Methode C — Ø1200 + overflow (Calcul_C)</t>
+          <t>Resultats Methode C — Ø1200 + Q_overflow (V via B25)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vmax_C (m3) = max(V_pond+V_ditch)</t>
+          <t>Vmax_C (m3) = max(V_total)</t>
         </is>
       </c>
       <c r="B48" s="13">
@@ -2167,29 +2186,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>• Plus d'aire de bassin: augmenter les surfaces jaunes sur Stage_Storage (et/ou Aire B24).</t>
+          <t>• Stage_Storage = Z1+Z2 (sans Ø900). Editer jaune; limite ville 37.40 m (B27 / ligne orange).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>• Methode A: 1re estimation. B: rating FHWA pipe. C: pipe + fosse si WSE depasse le crest.</t>
+          <t>• B25=0: V Methode C = leve seul. B25=1: +V_ditch trapeze. Q_overflow toujours actif si WSE&gt;crest.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>• Verifier la capacite/vitesse aval avec Qout(t) de Calcul_B ou C (pointe plus haute qu'avec Ø900).</t>
+          <t>• Methode A: 1re estimation. B: FHWA pipe (Aire B24). C: pipe + Q_overflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>• Verifier pointe aval (Ø1200 livre plus que l'ancien Ø900).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A2:F3"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
@@ -4921,7 +4948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4935,14 +4962,14 @@
     <row r="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Stage–storage du leve (bassin AGRANDI sans Ø900) — editer surfaces jaunes</t>
+          <t>Stage–storage COMBINE (Zone1+Zone2) — bassin SANS Ø900 — editer jaune</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Remplacez les aires par votre nouveau leve (plus d'aire attendue sans emprise Ø900). Surfaces jaunes synchronisees avec votre copie locale. Ligne 37.28 m: Role laisse vide (comme votre fichier local).</t>
+          <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Aires = somme Z1+Z2 du leve deux zones (scenario sans ponceau Ø900 intermediaire). Jaune = WSE et Surface editables (AutoCAD). Orange = 37.40 m limite ville. Ancien seuil etude 37.28 reste dans la table.</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5033,7 @@
         <v>35.5</v>
       </c>
       <c r="B12" s="10" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C12" s="28">
         <f>A12-A11</f>
@@ -5022,7 +5049,7 @@
       </c>
       <c r="F12" s="26" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer</t>
+          <t>Levé Z1+Z2 — éditer si AutoCAD diffère</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5058,7 @@
         <v>36.01</v>
       </c>
       <c r="B13" s="10" t="n">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C13" s="28">
         <f>A13-A12</f>
@@ -5047,7 +5074,7 @@
       </c>
       <c r="F13" s="26" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer</t>
+          <t>Levé Z1+Z2</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5083,7 @@
         <v>36.5</v>
       </c>
       <c r="B14" s="10" t="n">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="C14" s="28">
         <f>A14-A13</f>
@@ -5072,7 +5099,7 @@
       </c>
       <c r="F14" s="26" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer</t>
+          <t>Levé Z1+Z2</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5108,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="10" t="n">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="C15" s="28">
         <f>A15-A14</f>
@@ -5097,7 +5124,7 @@
       </c>
       <c r="F15" s="26" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer</t>
+          <t>Levé Z1+Z2</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5133,7 @@
         <v>37.28</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="C16" s="31">
         <f>A16-A15</f>
@@ -5120,30 +5147,34 @@
         <f>E15+D16</f>
         <v/>
       </c>
-      <c r="F16" s="33" t="n"/>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>Ancien seuil étude (+1.5 m) — référence</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="n">
+      <c r="A17" s="31" t="n">
         <v>37.4</v>
       </c>
       <c r="B17" s="10" t="n">
-        <v>1516</v>
-      </c>
-      <c r="C17" s="28">
+        <v>2320</v>
+      </c>
+      <c r="C17" s="31">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="32">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="32">
         <f>E16+D17</f>
         <v/>
       </c>
-      <c r="F17" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder — remplacer</t>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>LIMITE VILLE (WSE max + freeboard 0.6 m)</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5183,7 @@
         <v>40</v>
       </c>
       <c r="B18" s="10" t="n">
-        <v>3746</v>
+        <v>3732</v>
       </c>
       <c r="C18" s="28">
         <f>A18-A17</f>
@@ -5168,7 +5199,7 @@
       </c>
       <c r="F18" s="26" t="inlineStr">
         <is>
-          <t>Placeholder haut — remplacer</t>
+          <t>Sommet table</t>
         </is>
       </c>
     </row>
@@ -5205,12 +5236,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V @ 37.28 m</t>
+          <t>V @ 37.28 m (ancien seuil)</t>
         </is>
       </c>
       <c r="B23" s="34">
         <f>E16</f>
         <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>V @ 37.40 m (limite ville)</t>
+        </is>
+      </c>
+      <c r="B24" s="23">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Comparer a Vmax Methode C</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5234,14 +5281,14 @@
     <row r="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Methode C — Q_1200 + Q_overflow; V_pond + V_ditch</t>
+          <t>Methode C — Q_1200 + Q_overflow; V = V_pond (+ V_ditch si B25=1)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lie a Parametres (crest, b, n, z, S, L). Overflow si WSE &gt;= crest.</t>
+          <t>Lie a Parametres B25–B32. Q_overflow si WSE&gt;=crest. B25=0 → V_ditch=0 (leve seul).</t>
         </is>
       </c>
     </row>
@@ -5319,6 +5366,17 @@
       </c>
       <c r="B10" s="27">
         <f>Parametres!B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Inclure V_ditch</t>
+        </is>
+      </c>
+      <c r="B11" s="27">
+        <f>Parametres!B25</f>
         <v/>
       </c>
     </row>
@@ -5391,7 +5449,7 @@
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>D13*$B$9</f>
+        <f>IF($B$11=1,D13*$B$9,0)</f>
         <v/>
       </c>
       <c r="F13" s="18">
@@ -5399,7 +5457,7 @@
         <v/>
       </c>
       <c r="G13" s="24">
-        <f>E13+F13</f>
+        <f>F13+E13</f>
         <v/>
       </c>
       <c r="H13" s="19">
@@ -5432,7 +5490,7 @@
         <v/>
       </c>
       <c r="E14" s="18">
-        <f>D14*$B$9</f>
+        <f>IF($B$11=1,D14*$B$9,0)</f>
         <v/>
       </c>
       <c r="F14" s="18">
@@ -5440,7 +5498,7 @@
         <v/>
       </c>
       <c r="G14" s="24">
-        <f>E14+F14</f>
+        <f>F14+E14</f>
         <v/>
       </c>
       <c r="H14" s="19">
@@ -5473,7 +5531,7 @@
         <v/>
       </c>
       <c r="E15" s="18">
-        <f>D15*$B$9</f>
+        <f>IF($B$11=1,D15*$B$9,0)</f>
         <v/>
       </c>
       <c r="F15" s="18">
@@ -5481,7 +5539,7 @@
         <v/>
       </c>
       <c r="G15" s="24">
-        <f>E15+F15</f>
+        <f>F15+E15</f>
         <v/>
       </c>
       <c r="H15" s="19">
@@ -5514,7 +5572,7 @@
         <v/>
       </c>
       <c r="E16" s="18">
-        <f>D16*$B$9</f>
+        <f>IF($B$11=1,D16*$B$9,0)</f>
         <v/>
       </c>
       <c r="F16" s="18">
@@ -5522,7 +5580,7 @@
         <v/>
       </c>
       <c r="G16" s="24">
-        <f>E16+F16</f>
+        <f>F16+E16</f>
         <v/>
       </c>
       <c r="H16" s="19">
@@ -5555,7 +5613,7 @@
         <v/>
       </c>
       <c r="E17" s="18">
-        <f>D17*$B$9</f>
+        <f>IF($B$11=1,D17*$B$9,0)</f>
         <v/>
       </c>
       <c r="F17" s="18">
@@ -5563,7 +5621,7 @@
         <v/>
       </c>
       <c r="G17" s="24">
-        <f>E17+F17</f>
+        <f>F17+E17</f>
         <v/>
       </c>
       <c r="H17" s="19">
@@ -5596,7 +5654,7 @@
         <v/>
       </c>
       <c r="E18" s="18">
-        <f>D18*$B$9</f>
+        <f>IF($B$11=1,D18*$B$9,0)</f>
         <v/>
       </c>
       <c r="F18" s="18">
@@ -5604,7 +5662,7 @@
         <v/>
       </c>
       <c r="G18" s="24">
-        <f>E18+F18</f>
+        <f>F18+E18</f>
         <v/>
       </c>
       <c r="H18" s="19">
@@ -5637,7 +5695,7 @@
         <v/>
       </c>
       <c r="E19" s="18">
-        <f>D19*$B$9</f>
+        <f>IF($B$11=1,D19*$B$9,0)</f>
         <v/>
       </c>
       <c r="F19" s="18">
@@ -5645,7 +5703,7 @@
         <v/>
       </c>
       <c r="G19" s="24">
-        <f>E19+F19</f>
+        <f>F19+E19</f>
         <v/>
       </c>
       <c r="H19" s="19">
@@ -5678,7 +5736,7 @@
         <v/>
       </c>
       <c r="E20" s="18">
-        <f>D20*$B$9</f>
+        <f>IF($B$11=1,D20*$B$9,0)</f>
         <v/>
       </c>
       <c r="F20" s="18">
@@ -5686,7 +5744,7 @@
         <v/>
       </c>
       <c r="G20" s="24">
-        <f>E20+F20</f>
+        <f>F20+E20</f>
         <v/>
       </c>
       <c r="H20" s="19">
@@ -5719,7 +5777,7 @@
         <v/>
       </c>
       <c r="E21" s="18">
-        <f>D21*$B$9</f>
+        <f>IF($B$11=1,D21*$B$9,0)</f>
         <v/>
       </c>
       <c r="F21" s="18">
@@ -5727,7 +5785,7 @@
         <v/>
       </c>
       <c r="G21" s="24">
-        <f>E21+F21</f>
+        <f>F21+E21</f>
         <v/>
       </c>
       <c r="H21" s="19">
@@ -5760,7 +5818,7 @@
         <v/>
       </c>
       <c r="E22" s="18">
-        <f>D22*$B$9</f>
+        <f>IF($B$11=1,D22*$B$9,0)</f>
         <v/>
       </c>
       <c r="F22" s="18">
@@ -5768,7 +5826,7 @@
         <v/>
       </c>
       <c r="G22" s="24">
-        <f>E22+F22</f>
+        <f>F22+E22</f>
         <v/>
       </c>
       <c r="H22" s="19">
@@ -5801,7 +5859,7 @@
         <v/>
       </c>
       <c r="E23" s="18">
-        <f>D23*$B$9</f>
+        <f>IF($B$11=1,D23*$B$9,0)</f>
         <v/>
       </c>
       <c r="F23" s="18">
@@ -5809,7 +5867,7 @@
         <v/>
       </c>
       <c r="G23" s="24">
-        <f>E23+F23</f>
+        <f>F23+E23</f>
         <v/>
       </c>
       <c r="H23" s="19">
@@ -5842,7 +5900,7 @@
         <v/>
       </c>
       <c r="E24" s="18">
-        <f>D24*$B$9</f>
+        <f>IF($B$11=1,D24*$B$9,0)</f>
         <v/>
       </c>
       <c r="F24" s="18">
@@ -5850,7 +5908,7 @@
         <v/>
       </c>
       <c r="G24" s="24">
-        <f>E24+F24</f>
+        <f>F24+E24</f>
         <v/>
       </c>
       <c r="H24" s="19">
@@ -5883,7 +5941,7 @@
         <v/>
       </c>
       <c r="E25" s="18">
-        <f>D25*$B$9</f>
+        <f>IF($B$11=1,D25*$B$9,0)</f>
         <v/>
       </c>
       <c r="F25" s="18">
@@ -5891,7 +5949,7 @@
         <v/>
       </c>
       <c r="G25" s="24">
-        <f>E25+F25</f>
+        <f>F25+E25</f>
         <v/>
       </c>
       <c r="H25" s="19">
@@ -5924,7 +5982,7 @@
         <v/>
       </c>
       <c r="E26" s="18">
-        <f>D26*$B$9</f>
+        <f>IF($B$11=1,D26*$B$9,0)</f>
         <v/>
       </c>
       <c r="F26" s="18">
@@ -5932,7 +5990,7 @@
         <v/>
       </c>
       <c r="G26" s="24">
-        <f>E26+F26</f>
+        <f>F26+E26</f>
         <v/>
       </c>
       <c r="H26" s="19">
@@ -5965,7 +6023,7 @@
         <v/>
       </c>
       <c r="E27" s="18">
-        <f>D27*$B$9</f>
+        <f>IF($B$11=1,D27*$B$9,0)</f>
         <v/>
       </c>
       <c r="F27" s="18">
@@ -5973,7 +6031,7 @@
         <v/>
       </c>
       <c r="G27" s="24">
-        <f>E27+F27</f>
+        <f>F27+E27</f>
         <v/>
       </c>
       <c r="H27" s="19">
@@ -6006,7 +6064,7 @@
         <v/>
       </c>
       <c r="E28" s="18">
-        <f>D28*$B$9</f>
+        <f>IF($B$11=1,D28*$B$9,0)</f>
         <v/>
       </c>
       <c r="F28" s="18">
@@ -6014,7 +6072,7 @@
         <v/>
       </c>
       <c r="G28" s="24">
-        <f>E28+F28</f>
+        <f>F28+E28</f>
         <v/>
       </c>
       <c r="H28" s="19">
@@ -6047,7 +6105,7 @@
         <v/>
       </c>
       <c r="E29" s="18">
-        <f>D29*$B$9</f>
+        <f>IF($B$11=1,D29*$B$9,0)</f>
         <v/>
       </c>
       <c r="F29" s="18">
@@ -6055,7 +6113,7 @@
         <v/>
       </c>
       <c r="G29" s="24">
-        <f>E29+F29</f>
+        <f>F29+E29</f>
         <v/>
       </c>
       <c r="H29" s="19">
@@ -6088,7 +6146,7 @@
         <v/>
       </c>
       <c r="E30" s="18">
-        <f>D30*$B$9</f>
+        <f>IF($B$11=1,D30*$B$9,0)</f>
         <v/>
       </c>
       <c r="F30" s="18">
@@ -6096,7 +6154,7 @@
         <v/>
       </c>
       <c r="G30" s="24">
-        <f>E30+F30</f>
+        <f>F30+E30</f>
         <v/>
       </c>
       <c r="H30" s="19">
@@ -6129,7 +6187,7 @@
         <v/>
       </c>
       <c r="E31" s="18">
-        <f>D31*$B$9</f>
+        <f>IF($B$11=1,D31*$B$9,0)</f>
         <v/>
       </c>
       <c r="F31" s="18">
@@ -6137,7 +6195,7 @@
         <v/>
       </c>
       <c r="G31" s="24">
-        <f>E31+F31</f>
+        <f>F31+E31</f>
         <v/>
       </c>
       <c r="H31" s="19">
@@ -6170,7 +6228,7 @@
         <v/>
       </c>
       <c r="E32" s="18">
-        <f>D32*$B$9</f>
+        <f>IF($B$11=1,D32*$B$9,0)</f>
         <v/>
       </c>
       <c r="F32" s="18">
@@ -6178,7 +6236,7 @@
         <v/>
       </c>
       <c r="G32" s="24">
-        <f>E32+F32</f>
+        <f>F32+E32</f>
         <v/>
       </c>
       <c r="H32" s="19">
@@ -6211,7 +6269,7 @@
         <v/>
       </c>
       <c r="E33" s="18">
-        <f>D33*$B$9</f>
+        <f>IF($B$11=1,D33*$B$9,0)</f>
         <v/>
       </c>
       <c r="F33" s="18">
@@ -6219,7 +6277,7 @@
         <v/>
       </c>
       <c r="G33" s="24">
-        <f>E33+F33</f>
+        <f>F33+E33</f>
         <v/>
       </c>
       <c r="H33" s="19">
@@ -6252,7 +6310,7 @@
         <v/>
       </c>
       <c r="E34" s="18">
-        <f>D34*$B$9</f>
+        <f>IF($B$11=1,D34*$B$9,0)</f>
         <v/>
       </c>
       <c r="F34" s="18">
@@ -6260,7 +6318,7 @@
         <v/>
       </c>
       <c r="G34" s="24">
-        <f>E34+F34</f>
+        <f>F34+E34</f>
         <v/>
       </c>
       <c r="H34" s="19">
@@ -6293,7 +6351,7 @@
         <v/>
       </c>
       <c r="E35" s="18">
-        <f>D35*$B$9</f>
+        <f>IF($B$11=1,D35*$B$9,0)</f>
         <v/>
       </c>
       <c r="F35" s="18">
@@ -6301,7 +6359,7 @@
         <v/>
       </c>
       <c r="G35" s="24">
-        <f>E35+F35</f>
+        <f>F35+E35</f>
         <v/>
       </c>
       <c r="H35" s="19">
@@ -6334,7 +6392,7 @@
         <v/>
       </c>
       <c r="E36" s="18">
-        <f>D36*$B$9</f>
+        <f>IF($B$11=1,D36*$B$9,0)</f>
         <v/>
       </c>
       <c r="F36" s="18">
@@ -6342,7 +6400,7 @@
         <v/>
       </c>
       <c r="G36" s="24">
-        <f>E36+F36</f>
+        <f>F36+E36</f>
         <v/>
       </c>
       <c r="H36" s="19">
@@ -6375,7 +6433,7 @@
         <v/>
       </c>
       <c r="E37" s="18">
-        <f>D37*$B$9</f>
+        <f>IF($B$11=1,D37*$B$9,0)</f>
         <v/>
       </c>
       <c r="F37" s="18">
@@ -6383,7 +6441,7 @@
         <v/>
       </c>
       <c r="G37" s="24">
-        <f>E37+F37</f>
+        <f>F37+E37</f>
         <v/>
       </c>
       <c r="H37" s="19">
@@ -6416,7 +6474,7 @@
         <v/>
       </c>
       <c r="E38" s="18">
-        <f>D38*$B$9</f>
+        <f>IF($B$11=1,D38*$B$9,0)</f>
         <v/>
       </c>
       <c r="F38" s="18">
@@ -6424,7 +6482,7 @@
         <v/>
       </c>
       <c r="G38" s="24">
-        <f>E38+F38</f>
+        <f>F38+E38</f>
         <v/>
       </c>
       <c r="H38" s="19">
@@ -6457,7 +6515,7 @@
         <v/>
       </c>
       <c r="E39" s="18">
-        <f>D39*$B$9</f>
+        <f>IF($B$11=1,D39*$B$9,0)</f>
         <v/>
       </c>
       <c r="F39" s="18">
@@ -6465,7 +6523,7 @@
         <v/>
       </c>
       <c r="G39" s="24">
-        <f>E39+F39</f>
+        <f>F39+E39</f>
         <v/>
       </c>
       <c r="H39" s="19">
@@ -6498,7 +6556,7 @@
         <v/>
       </c>
       <c r="E40" s="18">
-        <f>D40*$B$9</f>
+        <f>IF($B$11=1,D40*$B$9,0)</f>
         <v/>
       </c>
       <c r="F40" s="18">
@@ -6506,7 +6564,7 @@
         <v/>
       </c>
       <c r="G40" s="24">
-        <f>E40+F40</f>
+        <f>F40+E40</f>
         <v/>
       </c>
       <c r="H40" s="19">
@@ -6539,7 +6597,7 @@
         <v/>
       </c>
       <c r="E41" s="18">
-        <f>D41*$B$9</f>
+        <f>IF($B$11=1,D41*$B$9,0)</f>
         <v/>
       </c>
       <c r="F41" s="18">
@@ -6547,7 +6605,7 @@
         <v/>
       </c>
       <c r="G41" s="24">
-        <f>E41+F41</f>
+        <f>F41+E41</f>
         <v/>
       </c>
       <c r="H41" s="19">
@@ -6580,7 +6638,7 @@
         <v/>
       </c>
       <c r="E42" s="18">
-        <f>D42*$B$9</f>
+        <f>IF($B$11=1,D42*$B$9,0)</f>
         <v/>
       </c>
       <c r="F42" s="18">
@@ -6588,7 +6646,7 @@
         <v/>
       </c>
       <c r="G42" s="24">
-        <f>E42+F42</f>
+        <f>F42+E42</f>
         <v/>
       </c>
       <c r="H42" s="19">
@@ -6621,7 +6679,7 @@
         <v/>
       </c>
       <c r="E43" s="18">
-        <f>D43*$B$9</f>
+        <f>IF($B$11=1,D43*$B$9,0)</f>
         <v/>
       </c>
       <c r="F43" s="18">
@@ -6629,7 +6687,7 @@
         <v/>
       </c>
       <c r="G43" s="24">
-        <f>E43+F43</f>
+        <f>F43+E43</f>
         <v/>
       </c>
       <c r="H43" s="19">
@@ -6662,7 +6720,7 @@
         <v/>
       </c>
       <c r="E44" s="18">
-        <f>D44*$B$9</f>
+        <f>IF($B$11=1,D44*$B$9,0)</f>
         <v/>
       </c>
       <c r="F44" s="18">
@@ -6670,7 +6728,7 @@
         <v/>
       </c>
       <c r="G44" s="24">
-        <f>E44+F44</f>
+        <f>F44+E44</f>
         <v/>
       </c>
       <c r="H44" s="19">
@@ -6703,7 +6761,7 @@
         <v/>
       </c>
       <c r="E45" s="18">
-        <f>D45*$B$9</f>
+        <f>IF($B$11=1,D45*$B$9,0)</f>
         <v/>
       </c>
       <c r="F45" s="18">
@@ -6711,7 +6769,7 @@
         <v/>
       </c>
       <c r="G45" s="24">
-        <f>E45+F45</f>
+        <f>F45+E45</f>
         <v/>
       </c>
       <c r="H45" s="19">
@@ -6744,7 +6802,7 @@
         <v/>
       </c>
       <c r="E46" s="18">
-        <f>D46*$B$9</f>
+        <f>IF($B$11=1,D46*$B$9,0)</f>
         <v/>
       </c>
       <c r="F46" s="18">
@@ -6752,7 +6810,7 @@
         <v/>
       </c>
       <c r="G46" s="24">
-        <f>E46+F46</f>
+        <f>F46+E46</f>
         <v/>
       </c>
       <c r="H46" s="19">
@@ -6785,7 +6843,7 @@
         <v/>
       </c>
       <c r="E47" s="18">
-        <f>D47*$B$9</f>
+        <f>IF($B$11=1,D47*$B$9,0)</f>
         <v/>
       </c>
       <c r="F47" s="18">
@@ -6793,7 +6851,7 @@
         <v/>
       </c>
       <c r="G47" s="24">
-        <f>E47+F47</f>
+        <f>F47+E47</f>
         <v/>
       </c>
       <c r="H47" s="19">
@@ -6826,7 +6884,7 @@
         <v/>
       </c>
       <c r="E48" s="18">
-        <f>D48*$B$9</f>
+        <f>IF($B$11=1,D48*$B$9,0)</f>
         <v/>
       </c>
       <c r="F48" s="18">
@@ -6834,7 +6892,7 @@
         <v/>
       </c>
       <c r="G48" s="24">
-        <f>E48+F48</f>
+        <f>F48+E48</f>
         <v/>
       </c>
       <c r="H48" s="19">
@@ -6867,7 +6925,7 @@
         <v/>
       </c>
       <c r="E49" s="18">
-        <f>D49*$B$9</f>
+        <f>IF($B$11=1,D49*$B$9,0)</f>
         <v/>
       </c>
       <c r="F49" s="18">
@@ -6875,7 +6933,7 @@
         <v/>
       </c>
       <c r="G49" s="24">
-        <f>E49+F49</f>
+        <f>F49+E49</f>
         <v/>
       </c>
       <c r="H49" s="19">
@@ -6908,7 +6966,7 @@
         <v/>
       </c>
       <c r="E50" s="18">
-        <f>D50*$B$9</f>
+        <f>IF($B$11=1,D50*$B$9,0)</f>
         <v/>
       </c>
       <c r="F50" s="18">
@@ -6916,7 +6974,7 @@
         <v/>
       </c>
       <c r="G50" s="24">
-        <f>E50+F50</f>
+        <f>F50+E50</f>
         <v/>
       </c>
       <c r="H50" s="19">
@@ -6949,7 +7007,7 @@
         <v/>
       </c>
       <c r="E51" s="18">
-        <f>D51*$B$9</f>
+        <f>IF($B$11=1,D51*$B$9,0)</f>
         <v/>
       </c>
       <c r="F51" s="18">
@@ -6957,7 +7015,7 @@
         <v/>
       </c>
       <c r="G51" s="24">
-        <f>E51+F51</f>
+        <f>F51+E51</f>
         <v/>
       </c>
       <c r="H51" s="19">
@@ -6990,7 +7048,7 @@
         <v/>
       </c>
       <c r="E52" s="18">
-        <f>D52*$B$9</f>
+        <f>IF($B$11=1,D52*$B$9,0)</f>
         <v/>
       </c>
       <c r="F52" s="18">
@@ -6998,7 +7056,7 @@
         <v/>
       </c>
       <c r="G52" s="24">
-        <f>E52+F52</f>
+        <f>F52+E52</f>
         <v/>
       </c>
       <c r="H52" s="19">
@@ -7031,7 +7089,7 @@
         <v/>
       </c>
       <c r="E53" s="18">
-        <f>D53*$B$9</f>
+        <f>IF($B$11=1,D53*$B$9,0)</f>
         <v/>
       </c>
       <c r="F53" s="18">
@@ -7039,7 +7097,7 @@
         <v/>
       </c>
       <c r="G53" s="24">
-        <f>E53+F53</f>
+        <f>F53+E53</f>
         <v/>
       </c>
       <c r="H53" s="19">
@@ -7072,7 +7130,7 @@
         <v/>
       </c>
       <c r="E54" s="18">
-        <f>D54*$B$9</f>
+        <f>IF($B$11=1,D54*$B$9,0)</f>
         <v/>
       </c>
       <c r="F54" s="18">
@@ -7080,7 +7138,7 @@
         <v/>
       </c>
       <c r="G54" s="24">
-        <f>E54+F54</f>
+        <f>F54+E54</f>
         <v/>
       </c>
       <c r="H54" s="19">
@@ -7113,7 +7171,7 @@
         <v/>
       </c>
       <c r="E55" s="18">
-        <f>D55*$B$9</f>
+        <f>IF($B$11=1,D55*$B$9,0)</f>
         <v/>
       </c>
       <c r="F55" s="18">
@@ -7121,7 +7179,7 @@
         <v/>
       </c>
       <c r="G55" s="24">
-        <f>E55+F55</f>
+        <f>F55+E55</f>
         <v/>
       </c>
       <c r="H55" s="19">
@@ -7154,7 +7212,7 @@
         <v/>
       </c>
       <c r="E56" s="18">
-        <f>D56*$B$9</f>
+        <f>IF($B$11=1,D56*$B$9,0)</f>
         <v/>
       </c>
       <c r="F56" s="18">
@@ -7162,7 +7220,7 @@
         <v/>
       </c>
       <c r="G56" s="24">
-        <f>E56+F56</f>
+        <f>F56+E56</f>
         <v/>
       </c>
       <c r="H56" s="19">
@@ -7195,7 +7253,7 @@
         <v/>
       </c>
       <c r="E57" s="18">
-        <f>D57*$B$9</f>
+        <f>IF($B$11=1,D57*$B$9,0)</f>
         <v/>
       </c>
       <c r="F57" s="18">
@@ -7203,7 +7261,7 @@
         <v/>
       </c>
       <c r="G57" s="24">
-        <f>E57+F57</f>
+        <f>F57+E57</f>
         <v/>
       </c>
       <c r="H57" s="19">
@@ -7236,7 +7294,7 @@
         <v/>
       </c>
       <c r="E58" s="18">
-        <f>D58*$B$9</f>
+        <f>IF($B$11=1,D58*$B$9,0)</f>
         <v/>
       </c>
       <c r="F58" s="18">
@@ -7244,7 +7302,7 @@
         <v/>
       </c>
       <c r="G58" s="24">
-        <f>E58+F58</f>
+        <f>F58+E58</f>
         <v/>
       </c>
       <c r="H58" s="19">
@@ -7277,7 +7335,7 @@
         <v/>
       </c>
       <c r="E59" s="18">
-        <f>D59*$B$9</f>
+        <f>IF($B$11=1,D59*$B$9,0)</f>
         <v/>
       </c>
       <c r="F59" s="18">
@@ -7285,7 +7343,7 @@
         <v/>
       </c>
       <c r="G59" s="24">
-        <f>E59+F59</f>
+        <f>F59+E59</f>
         <v/>
       </c>
       <c r="H59" s="19">
@@ -7318,7 +7376,7 @@
         <v/>
       </c>
       <c r="E60" s="18">
-        <f>D60*$B$9</f>
+        <f>IF($B$11=1,D60*$B$9,0)</f>
         <v/>
       </c>
       <c r="F60" s="18">
@@ -7326,7 +7384,7 @@
         <v/>
       </c>
       <c r="G60" s="24">
-        <f>E60+F60</f>
+        <f>F60+E60</f>
         <v/>
       </c>
       <c r="H60" s="19">
@@ -7359,7 +7417,7 @@
         <v/>
       </c>
       <c r="E61" s="18">
-        <f>D61*$B$9</f>
+        <f>IF($B$11=1,D61*$B$9,0)</f>
         <v/>
       </c>
       <c r="F61" s="18">
@@ -7367,7 +7425,7 @@
         <v/>
       </c>
       <c r="G61" s="24">
-        <f>E61+F61</f>
+        <f>F61+E61</f>
         <v/>
       </c>
       <c r="H61" s="19">
@@ -7400,7 +7458,7 @@
         <v/>
       </c>
       <c r="E62" s="18">
-        <f>D62*$B$9</f>
+        <f>IF($B$11=1,D62*$B$9,0)</f>
         <v/>
       </c>
       <c r="F62" s="18">
@@ -7408,7 +7466,7 @@
         <v/>
       </c>
       <c r="G62" s="24">
-        <f>E62+F62</f>
+        <f>F62+E62</f>
         <v/>
       </c>
       <c r="H62" s="19">
@@ -7441,7 +7499,7 @@
         <v/>
       </c>
       <c r="E63" s="18">
-        <f>D63*$B$9</f>
+        <f>IF($B$11=1,D63*$B$9,0)</f>
         <v/>
       </c>
       <c r="F63" s="18">
@@ -7449,7 +7507,7 @@
         <v/>
       </c>
       <c r="G63" s="24">
-        <f>E63+F63</f>
+        <f>F63+E63</f>
         <v/>
       </c>
       <c r="H63" s="19">
@@ -7482,7 +7540,7 @@
         <v/>
       </c>
       <c r="E64" s="18">
-        <f>D64*$B$9</f>
+        <f>IF($B$11=1,D64*$B$9,0)</f>
         <v/>
       </c>
       <c r="F64" s="18">
@@ -7490,7 +7548,7 @@
         <v/>
       </c>
       <c r="G64" s="24">
-        <f>E64+F64</f>
+        <f>F64+E64</f>
         <v/>
       </c>
       <c r="H64" s="19">
@@ -7534,7 +7592,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WSE depuis V_total (Compose_1200); Qout = Q_1200 + Q_overflow.</t>
+          <t>WSE depuis V_total (Compose_1200; B25 pilote V_ditch). Qout = Q_1200 + Q_overflow.</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Le Ø900 est elimine: plus de controle etroit; le bassin peut etre agrandi (Stage_Storage).</t>
+          <t>1. Le Ø900 est elimine: controle = Ø1200; Stage_Storage = aires Z1+Z2 (leve combine).</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8135,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   C) Qout = Q_1200 + overflow trapèze au-dessus du crest (berme/fosse).</t>
+          <t xml:space="preserve">   C) Qout = Q_1200 + Q_overflow; V = leve (+ V_ditch si Parametres B25=1).</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,15 +133,16 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1682,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2211,10 +2212,123 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Vitesses de reference — V = Q / A_plein</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sans Ø900: control = Ø1200. V_eq = Q/A_plein. Partiellement rempli: V reelle = Q/A(h) plus elevee — voir Courbe_QH_1200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>Ouvrage</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>D (m)</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>A_plein (m2)</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>Q ref</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>V_eq (m/s)</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>Ø1500 (entree)</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C95" s="19">
+        <f>PI()*B95^2/4</f>
+        <v/>
+      </c>
+      <c r="D95" s="19">
+        <f>Hydrogramme!B4</f>
+        <v/>
+      </c>
+      <c r="E95" s="20">
+        <f>IF(C95&lt;=0,0,D95/C95)</f>
+        <v/>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>Qpointe</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>Ø1200 (controle)</t>
+        </is>
+      </c>
+      <c r="B96" s="18">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="C96" s="19">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="D96" s="19">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="E96" s="20">
+        <f>IF(C96&lt;=0,0,D96/C96)</f>
+        <v/>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Q_plein Manning</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>V_Ø1200 @ Qout Calcul_A (m/s)</t>
+        </is>
+      </c>
+      <c r="B97" s="14">
+        <f>IF(C96&lt;=0,0,Calcul_A!B2/C96)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A2:F3"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A56:F56"/>
@@ -2333,7 +2447,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="21" t="n">
         <v>0</v>
       </c>
       <c r="B7" s="19" t="n">
@@ -2345,7 +2459,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="n">
@@ -2357,7 +2471,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="21" t="n">
         <v>10</v>
       </c>
       <c r="B9" s="19" t="n">
@@ -2369,7 +2483,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="21" t="n">
         <v>15</v>
       </c>
       <c r="B10" s="19" t="n">
@@ -2381,7 +2495,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="21" t="n">
         <v>20</v>
       </c>
       <c r="B11" s="19" t="n">
@@ -2393,19 +2507,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="21" t="n">
         <v>22.5</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="22">
         <f>B12*$B$4</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="21" t="n">
         <v>27.5</v>
       </c>
       <c r="B13" s="19" t="n">
@@ -2417,7 +2531,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="21" t="n">
         <v>32.5</v>
       </c>
       <c r="B14" s="19" t="n">
@@ -2429,7 +2543,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="21" t="n">
         <v>37.5</v>
       </c>
       <c r="B15" s="19" t="n">
@@ -2441,7 +2555,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="21" t="n">
         <v>42.5</v>
       </c>
       <c r="B16" s="19" t="n">
@@ -2453,7 +2567,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="21" t="n">
         <v>47.5</v>
       </c>
       <c r="B17" s="19" t="n">
@@ -2465,7 +2579,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="21" t="n">
         <v>52.5</v>
       </c>
       <c r="B18" s="19" t="n">
@@ -2477,7 +2591,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="21" t="n">
         <v>57.5</v>
       </c>
       <c r="B19" s="19" t="n">
@@ -2494,7 +2608,7 @@
           <t>Qin max</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="23">
         <f>MAX(C7:C19)</f>
         <v/>
       </c>
@@ -2514,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2530,7 +2644,7 @@
           <t>Qout</t>
         </is>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="24">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2541,7 +2655,7 @@
           <t>Vmax_A (m3)</t>
         </is>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="25">
         <f>MAX(E8:E20)</f>
         <v/>
       </c>
@@ -2570,6 +2684,11 @@
       <c r="E7" s="17" t="inlineStr">
         <is>
           <t>V (m3)</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>V_Ø1200 (m/s)</t>
         </is>
       </c>
     </row>
@@ -2586,11 +2705,15 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="26" t="n">
         <v>0</v>
+      </c>
+      <c r="F8" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C8/Parametres!$C$96)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2606,12 +2729,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="21">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="26">
         <f>MAX(0,E8+(0.5*(B8+B9)-C9)*D9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C9/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2628,12 +2755,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="21">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="26">
         <f>MAX(0,E9+(0.5*(B9+B10)-C10)*D10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C10/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2650,12 +2781,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="21">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="26">
         <f>MAX(0,E10+(0.5*(B10+B11)-C11)*D11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C11/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2672,12 +2807,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="21">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="26">
         <f>MAX(0,E11+(0.5*(B11+B12)-C12)*D12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C12/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2694,12 +2833,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="21">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="26">
         <f>MAX(0,E12+(0.5*(B12+B13)-C13)*D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C13/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2716,12 +2859,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="21">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="26">
         <f>MAX(0,E13+(0.5*(B13+B14)-C14)*D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C14/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2738,12 +2885,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="21">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="26">
         <f>MAX(0,E14+(0.5*(B14+B15)-C15)*D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C15/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2760,12 +2911,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="21">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="26">
         <f>MAX(0,E15+(0.5*(B15+B16)-C16)*D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C16/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2782,12 +2937,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="21">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="26">
         <f>MAX(0,E16+(0.5*(B16+B17)-C17)*D17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C17/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2804,12 +2963,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="21">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="26">
         <f>MAX(0,E17+(0.5*(B17+B18)-C18)*D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C18/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2826,12 +2989,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="21">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="26">
         <f>MAX(0,E18+(0.5*(B18+B19)-C19)*D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C19/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2848,12 +3015,16 @@
         <f>$B$2</f>
         <v/>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="21">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="26">
         <f>MAX(0,E19+(0.5*(B19+B20)-C20)*D20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,C20/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2908,22 +3079,22 @@
           <t>K</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="27" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -2939,24 +3110,24 @@
         <f>Parametres!B11</f>
         <v/>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
       </c>
-      <c r="F5" s="26" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.0098</v>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="18" t="n">
         <v>0.0398</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="18" t="n">
         <v>0.67</v>
       </c>
-      <c r="J5" s="26" t="n">
+      <c r="J5" s="18" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2970,24 +3141,24 @@
         <f>Parametres!B12</f>
         <v/>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>beveled</t>
         </is>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.0018</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="18" t="n">
         <v>0.03</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="18" t="n">
         <v>0.74</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="18" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -3001,24 +3172,24 @@
         <f>Parametres!B13</f>
         <v/>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>groove_headwall</t>
         </is>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.0078</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="18" t="n">
         <v>0.0292</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="18" t="n">
         <v>0.74</v>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="18" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -3050,7 +3221,7 @@
           <t>TW au-dessus Zout (m)</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3060,7 +3231,7 @@
           <t>Entree</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -3152,12 +3323,22 @@
           <t>Q gouvernant</t>
         </is>
       </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>A_ecoul (m2)</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>V_gouv (m/s)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="n">
+      <c r="A20" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="29">
         <f>$B$7+A20</f>
         <v/>
       </c>
@@ -3173,17 +3354,25 @@
         <f>MIN(C20,D20)</f>
         <v/>
       </c>
+      <c r="F20" s="19">
+        <f>IF(A20&lt;=0,0,IF(A20&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A20/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A20/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>IF(F20&lt;=0,0,E20/F20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="n">
+      <c r="A21" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>$B$7+A21</f>
         <v/>
       </c>
       <c r="C21" s="19">
-        <f>IF(A21&lt;=0,0,IF(A21&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A21/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A21/$B$5-$B$16)/5)))))</f>
+        <f>IF(A21&lt;=0,0,IF(A21&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A21/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A21/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D21" s="19">
@@ -3194,17 +3383,25 @@
         <f>MIN(C21,D21)</f>
         <v/>
       </c>
+      <c r="F21" s="19">
+        <f>IF(A21&lt;=0,0,IF(A21&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A21/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A21/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="20">
+        <f>IF(F21&lt;=0,0,E21/F21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="29">
         <f>$B$7+A22</f>
         <v/>
       </c>
       <c r="C22" s="19">
-        <f>IF(A22&lt;=0,0,IF(A22&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A22/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A22/$B$5-$B$16)/5)))))</f>
+        <f>IF(A22&lt;=0,0,IF(A22&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A22/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A22/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D22" s="19">
@@ -3215,17 +3412,25 @@
         <f>MIN(C22,D22)</f>
         <v/>
       </c>
+      <c r="F22" s="19">
+        <f>IF(A22&lt;=0,0,IF(A22&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A22/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A22/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
+        <f>IF(F22&lt;=0,0,E22/F22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="n">
+      <c r="A23" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>$B$7+A23</f>
         <v/>
       </c>
       <c r="C23" s="19">
-        <f>IF(A23&lt;=0,0,IF(A23&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A23/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A23/$B$5-$B$16)/5)))))</f>
+        <f>IF(A23&lt;=0,0,IF(A23&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A23/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A23/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D23" s="19">
@@ -3236,17 +3441,25 @@
         <f>MIN(C23,D23)</f>
         <v/>
       </c>
+      <c r="F23" s="19">
+        <f>IF(A23&lt;=0,0,IF(A23&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A23/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A23/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>IF(F23&lt;=0,0,E23/F23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="n">
+      <c r="A24" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="29">
         <f>$B$7+A24</f>
         <v/>
       </c>
       <c r="C24" s="19">
-        <f>IF(A24&lt;=0,0,IF(A24&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A24/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A24/$B$5-$B$16)/5)))))</f>
+        <f>IF(A24&lt;=0,0,IF(A24&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A24/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A24/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D24" s="19">
@@ -3257,17 +3470,25 @@
         <f>MIN(C24,D24)</f>
         <v/>
       </c>
+      <c r="F24" s="19">
+        <f>IF(A24&lt;=0,0,IF(A24&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A24/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A24/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="20">
+        <f>IF(F24&lt;=0,0,E24/F24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="n">
+      <c r="A25" s="29" t="n">
         <v>0.25</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <f>$B$7+A25</f>
         <v/>
       </c>
       <c r="C25" s="19">
-        <f>IF(A25&lt;=0,0,IF(A25&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A25/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A25/$B$5-$B$16)/5)))))</f>
+        <f>IF(A25&lt;=0,0,IF(A25&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A25/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A25/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D25" s="19">
@@ -3278,17 +3499,25 @@
         <f>MIN(C25,D25)</f>
         <v/>
       </c>
+      <c r="F25" s="19">
+        <f>IF(A25&lt;=0,0,IF(A25&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A25/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A25/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="20">
+        <f>IF(F25&lt;=0,0,E25/F25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="n">
+      <c r="A26" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="29">
         <f>$B$7+A26</f>
         <v/>
       </c>
       <c r="C26" s="19">
-        <f>IF(A26&lt;=0,0,IF(A26&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A26/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A26/$B$5-$B$16)/5)))))</f>
+        <f>IF(A26&lt;=0,0,IF(A26&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A26/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A26/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D26" s="19">
@@ -3299,17 +3528,25 @@
         <f>MIN(C26,D26)</f>
         <v/>
       </c>
+      <c r="F26" s="19">
+        <f>IF(A26&lt;=0,0,IF(A26&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A26/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A26/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="20">
+        <f>IF(F26&lt;=0,0,E26/F26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="n">
+      <c r="A27" s="29" t="n">
         <v>0.35</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="29">
         <f>$B$7+A27</f>
         <v/>
       </c>
       <c r="C27" s="19">
-        <f>IF(A27&lt;=0,0,IF(A27&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A27/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A27/$B$5-$B$16)/5)))))</f>
+        <f>IF(A27&lt;=0,0,IF(A27&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A27/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A27/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D27" s="19">
@@ -3320,17 +3557,25 @@
         <f>MIN(C27,D27)</f>
         <v/>
       </c>
+      <c r="F27" s="19">
+        <f>IF(A27&lt;=0,0,IF(A27&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A27/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A27/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="20">
+        <f>IF(F27&lt;=0,0,E27/F27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="n">
+      <c r="A28" s="29" t="n">
         <v>0.4</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="29">
         <f>$B$7+A28</f>
         <v/>
       </c>
       <c r="C28" s="19">
-        <f>IF(A28&lt;=0,0,IF(A28&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A28/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A28/$B$5-$B$16)/5)))))</f>
+        <f>IF(A28&lt;=0,0,IF(A28&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A28/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A28/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D28" s="19">
@@ -3341,17 +3586,25 @@
         <f>MIN(C28,D28)</f>
         <v/>
       </c>
+      <c r="F28" s="19">
+        <f>IF(A28&lt;=0,0,IF(A28&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A28/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A28/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="20">
+        <f>IF(F28&lt;=0,0,E28/F28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="n">
+      <c r="A29" s="29" t="n">
         <v>0.45</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="29">
         <f>$B$7+A29</f>
         <v/>
       </c>
       <c r="C29" s="19">
-        <f>IF(A29&lt;=0,0,IF(A29&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A29/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A29/$B$5-$B$16)/5)))))</f>
+        <f>IF(A29&lt;=0,0,IF(A29&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A29/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A29/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D29" s="19">
@@ -3362,17 +3615,25 @@
         <f>MIN(C29,D29)</f>
         <v/>
       </c>
+      <c r="F29" s="19">
+        <f>IF(A29&lt;=0,0,IF(A29&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A29/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A29/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="20">
+        <f>IF(F29&lt;=0,0,E29/F29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="29">
         <f>$B$7+A30</f>
         <v/>
       </c>
       <c r="C30" s="19">
-        <f>IF(A30&lt;=0,0,IF(A30&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A30/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A30/$B$5-$B$16)/5)))))</f>
+        <f>IF(A30&lt;=0,0,IF(A30&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A30/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A30/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D30" s="19">
@@ -3383,17 +3644,25 @@
         <f>MIN(C30,D30)</f>
         <v/>
       </c>
+      <c r="F30" s="19">
+        <f>IF(A30&lt;=0,0,IF(A30&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A30/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A30/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G30" s="20">
+        <f>IF(F30&lt;=0,0,E30/F30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="29" t="n">
         <v>0.55</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="29">
         <f>$B$7+A31</f>
         <v/>
       </c>
       <c r="C31" s="19">
-        <f>IF(A31&lt;=0,0,IF(A31&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A31/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A31/$B$5-$B$16)/5)))))</f>
+        <f>IF(A31&lt;=0,0,IF(A31&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A31/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A31/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D31" s="19">
@@ -3404,17 +3673,25 @@
         <f>MIN(C31,D31)</f>
         <v/>
       </c>
+      <c r="F31" s="19">
+        <f>IF(A31&lt;=0,0,IF(A31&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A31/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A31/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G31" s="20">
+        <f>IF(F31&lt;=0,0,E31/F31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="n">
+      <c r="A32" s="29" t="n">
         <v>0.6</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="29">
         <f>$B$7+A32</f>
         <v/>
       </c>
       <c r="C32" s="19">
-        <f>IF(A32&lt;=0,0,IF(A32&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A32/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A32/$B$5-$B$16)/5)))))</f>
+        <f>IF(A32&lt;=0,0,IF(A32&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A32/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A32/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D32" s="19">
@@ -3425,17 +3702,25 @@
         <f>MIN(C32,D32)</f>
         <v/>
       </c>
+      <c r="F32" s="19">
+        <f>IF(A32&lt;=0,0,IF(A32&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A32/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A32/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G32" s="20">
+        <f>IF(F32&lt;=0,0,E32/F32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="n">
+      <c r="A33" s="29" t="n">
         <v>0.65</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="29">
         <f>$B$7+A33</f>
         <v/>
       </c>
       <c r="C33" s="19">
-        <f>IF(A33&lt;=0,0,IF(A33&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A33/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A33/$B$5-$B$16)/5)))))</f>
+        <f>IF(A33&lt;=0,0,IF(A33&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A33/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A33/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D33" s="19">
@@ -3446,17 +3731,25 @@
         <f>MIN(C33,D33)</f>
         <v/>
       </c>
+      <c r="F33" s="19">
+        <f>IF(A33&lt;=0,0,IF(A33&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A33/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A33/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G33" s="20">
+        <f>IF(F33&lt;=0,0,E33/F33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="n">
+      <c r="A34" s="29" t="n">
         <v>0.7</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="29">
         <f>$B$7+A34</f>
         <v/>
       </c>
       <c r="C34" s="19">
-        <f>IF(A34&lt;=0,0,IF(A34&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A34/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A34/$B$5-$B$16)/5)))))</f>
+        <f>IF(A34&lt;=0,0,IF(A34&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A34/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A34/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D34" s="19">
@@ -3467,17 +3760,25 @@
         <f>MIN(C34,D34)</f>
         <v/>
       </c>
+      <c r="F34" s="19">
+        <f>IF(A34&lt;=0,0,IF(A34&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A34/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A34/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G34" s="20">
+        <f>IF(F34&lt;=0,0,E34/F34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="n">
+      <c r="A35" s="29" t="n">
         <v>0.75</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="29">
         <f>$B$7+A35</f>
         <v/>
       </c>
       <c r="C35" s="19">
-        <f>IF(A35&lt;=0,0,IF(A35&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A35/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A35/$B$5-$B$16)/5)))))</f>
+        <f>IF(A35&lt;=0,0,IF(A35&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A35/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A35/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D35" s="19">
@@ -3488,17 +3789,25 @@
         <f>MIN(C35,D35)</f>
         <v/>
       </c>
+      <c r="F35" s="19">
+        <f>IF(A35&lt;=0,0,IF(A35&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A35/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A35/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G35" s="20">
+        <f>IF(F35&lt;=0,0,E35/F35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="n">
+      <c r="A36" s="29" t="n">
         <v>0.8</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="29">
         <f>$B$7+A36</f>
         <v/>
       </c>
       <c r="C36" s="19">
-        <f>IF(A36&lt;=0,0,IF(A36&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A36/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A36/$B$5-$B$16)/5)))))</f>
+        <f>IF(A36&lt;=0,0,IF(A36&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A36/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A36/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D36" s="19">
@@ -3509,17 +3818,25 @@
         <f>MIN(C36,D36)</f>
         <v/>
       </c>
+      <c r="F36" s="19">
+        <f>IF(A36&lt;=0,0,IF(A36&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A36/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A36/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G36" s="20">
+        <f>IF(F36&lt;=0,0,E36/F36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="n">
+      <c r="A37" s="29" t="n">
         <v>0.85</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="29">
         <f>$B$7+A37</f>
         <v/>
       </c>
       <c r="C37" s="19">
-        <f>IF(A37&lt;=0,0,IF(A37&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A37/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A37/$B$5-$B$16)/5)))))</f>
+        <f>IF(A37&lt;=0,0,IF(A37&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A37/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A37/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D37" s="19">
@@ -3530,17 +3847,25 @@
         <f>MIN(C37,D37)</f>
         <v/>
       </c>
+      <c r="F37" s="19">
+        <f>IF(A37&lt;=0,0,IF(A37&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A37/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A37/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G37" s="20">
+        <f>IF(F37&lt;=0,0,E37/F37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="n">
+      <c r="A38" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="29">
         <f>$B$7+A38</f>
         <v/>
       </c>
       <c r="C38" s="19">
-        <f>IF(A38&lt;=0,0,IF(A38&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A38/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A38/$B$5-$B$16)/5)))))</f>
+        <f>IF(A38&lt;=0,0,IF(A38&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A38/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A38/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D38" s="19">
@@ -3551,17 +3876,25 @@
         <f>MIN(C38,D38)</f>
         <v/>
       </c>
+      <c r="F38" s="19">
+        <f>IF(A38&lt;=0,0,IF(A38&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A38/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A38/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G38" s="20">
+        <f>IF(F38&lt;=0,0,E38/F38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="n">
+      <c r="A39" s="29" t="n">
         <v>0.95</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="29">
         <f>$B$7+A39</f>
         <v/>
       </c>
       <c r="C39" s="19">
-        <f>IF(A39&lt;=0,0,IF(A39&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A39/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A39/$B$5-$B$16)/5)))))</f>
+        <f>IF(A39&lt;=0,0,IF(A39&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A39/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A39/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D39" s="19">
@@ -3572,17 +3905,25 @@
         <f>MIN(C39,D39)</f>
         <v/>
       </c>
+      <c r="F39" s="19">
+        <f>IF(A39&lt;=0,0,IF(A39&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A39/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A39/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G39" s="20">
+        <f>IF(F39&lt;=0,0,E39/F39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="n">
+      <c r="A40" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="29">
         <f>$B$7+A40</f>
         <v/>
       </c>
       <c r="C40" s="19">
-        <f>IF(A40&lt;=0,0,IF(A40&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A40/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A40/$B$5-$B$16)/5)))))</f>
+        <f>IF(A40&lt;=0,0,IF(A40&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A40/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A40/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D40" s="19">
@@ -3593,17 +3934,25 @@
         <f>MIN(C40,D40)</f>
         <v/>
       </c>
+      <c r="F40" s="19">
+        <f>IF(A40&lt;=0,0,IF(A40&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A40/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A40/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G40" s="20">
+        <f>IF(F40&lt;=0,0,E40/F40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="n">
+      <c r="A41" s="29" t="n">
         <v>1.05</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="29">
         <f>$B$7+A41</f>
         <v/>
       </c>
       <c r="C41" s="19">
-        <f>IF(A41&lt;=0,0,IF(A41&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A41/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A41/$B$5-$B$16)/5)))))</f>
+        <f>IF(A41&lt;=0,0,IF(A41&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A41/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A41/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D41" s="19">
@@ -3614,17 +3963,25 @@
         <f>MIN(C41,D41)</f>
         <v/>
       </c>
+      <c r="F41" s="19">
+        <f>IF(A41&lt;=0,0,IF(A41&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A41/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A41/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G41" s="20">
+        <f>IF(F41&lt;=0,0,E41/F41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n">
+      <c r="A42" s="29" t="n">
         <v>1.1</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="29">
         <f>$B$7+A42</f>
         <v/>
       </c>
       <c r="C42" s="19">
-        <f>IF(A42&lt;=0,0,IF(A42&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A42/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A42/$B$5-$B$16)/5)))))</f>
+        <f>IF(A42&lt;=0,0,IF(A42&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A42/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A42/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D42" s="19">
@@ -3635,17 +3992,25 @@
         <f>MIN(C42,D42)</f>
         <v/>
       </c>
+      <c r="F42" s="19">
+        <f>IF(A42&lt;=0,0,IF(A42&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A42/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A42/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G42" s="20">
+        <f>IF(F42&lt;=0,0,E42/F42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="n">
+      <c r="A43" s="29" t="n">
         <v>1.15</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="29">
         <f>$B$7+A43</f>
         <v/>
       </c>
       <c r="C43" s="19">
-        <f>IF(A43&lt;=0,0,IF(A43&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A43/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A43/$B$5-$B$16)/5)))))</f>
+        <f>IF(A43&lt;=0,0,IF(A43&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A43/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A43/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D43" s="19">
@@ -3656,17 +4021,25 @@
         <f>MIN(C43,D43)</f>
         <v/>
       </c>
+      <c r="F43" s="19">
+        <f>IF(A43&lt;=0,0,IF(A43&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A43/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A43/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G43" s="20">
+        <f>IF(F43&lt;=0,0,E43/F43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="n">
+      <c r="A44" s="29" t="n">
         <v>1.2</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="29">
         <f>$B$7+A44</f>
         <v/>
       </c>
       <c r="C44" s="19">
-        <f>IF(A44&lt;=0,0,IF(A44&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A44/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A44/$B$5-$B$16)/5)))))</f>
+        <f>IF(A44&lt;=0,0,IF(A44&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A44/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A44/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D44" s="19">
@@ -3677,17 +4050,25 @@
         <f>MIN(C44,D44)</f>
         <v/>
       </c>
+      <c r="F44" s="19">
+        <f>IF(A44&lt;=0,0,IF(A44&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A44/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A44/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G44" s="20">
+        <f>IF(F44&lt;=0,0,E44/F44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="28" t="n">
+      <c r="A45" s="29" t="n">
         <v>1.25</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="29">
         <f>$B$7+A45</f>
         <v/>
       </c>
       <c r="C45" s="19">
-        <f>IF(A45&lt;=0,0,IF(A45&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A45/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A45/$B$5-$B$16)/5)))))</f>
+        <f>IF(A45&lt;=0,0,IF(A45&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A45/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A45/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D45" s="19">
@@ -3698,17 +4079,25 @@
         <f>MIN(C45,D45)</f>
         <v/>
       </c>
+      <c r="F45" s="19">
+        <f>IF(A45&lt;=0,0,IF(A45&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A45/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A45/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G45" s="20">
+        <f>IF(F45&lt;=0,0,E45/F45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="28" t="n">
+      <c r="A46" s="29" t="n">
         <v>1.3</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="29">
         <f>$B$7+A46</f>
         <v/>
       </c>
       <c r="C46" s="19">
-        <f>IF(A46&lt;=0,0,IF(A46&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A46/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A46/$B$5-$B$16)/5)))))</f>
+        <f>IF(A46&lt;=0,0,IF(A46&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A46/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A46/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D46" s="19">
@@ -3719,17 +4108,25 @@
         <f>MIN(C46,D46)</f>
         <v/>
       </c>
+      <c r="F46" s="19">
+        <f>IF(A46&lt;=0,0,IF(A46&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A46/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A46/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G46" s="20">
+        <f>IF(F46&lt;=0,0,E46/F46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="28" t="n">
+      <c r="A47" s="29" t="n">
         <v>1.35</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="29">
         <f>$B$7+A47</f>
         <v/>
       </c>
       <c r="C47" s="19">
-        <f>IF(A47&lt;=0,0,IF(A47&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A47/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A47/$B$5-$B$16)/5)))))</f>
+        <f>IF(A47&lt;=0,0,IF(A47&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A47/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A47/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D47" s="19">
@@ -3740,17 +4137,25 @@
         <f>MIN(C47,D47)</f>
         <v/>
       </c>
+      <c r="F47" s="19">
+        <f>IF(A47&lt;=0,0,IF(A47&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A47/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A47/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G47" s="20">
+        <f>IF(F47&lt;=0,0,E47/F47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="n">
+      <c r="A48" s="29" t="n">
         <v>1.4</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="29">
         <f>$B$7+A48</f>
         <v/>
       </c>
       <c r="C48" s="19">
-        <f>IF(A48&lt;=0,0,IF(A48&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A48/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A48/$B$5-$B$16)/5)))))</f>
+        <f>IF(A48&lt;=0,0,IF(A48&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A48/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A48/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D48" s="19">
@@ -3761,17 +4166,25 @@
         <f>MIN(C48,D48)</f>
         <v/>
       </c>
+      <c r="F48" s="19">
+        <f>IF(A48&lt;=0,0,IF(A48&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A48/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A48/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G48" s="20">
+        <f>IF(F48&lt;=0,0,E48/F48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="28" t="n">
+      <c r="A49" s="29" t="n">
         <v>1.45</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="29">
         <f>$B$7+A49</f>
         <v/>
       </c>
       <c r="C49" s="19">
-        <f>IF(A49&lt;=0,0,IF(A49&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A49/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A49/$B$5-$B$16)/5)))))</f>
+        <f>IF(A49&lt;=0,0,IF(A49&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A49/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A49/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D49" s="19">
@@ -3782,17 +4195,25 @@
         <f>MIN(C49,D49)</f>
         <v/>
       </c>
+      <c r="F49" s="19">
+        <f>IF(A49&lt;=0,0,IF(A49&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A49/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A49/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G49" s="20">
+        <f>IF(F49&lt;=0,0,E49/F49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="n">
+      <c r="A50" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="29">
         <f>$B$7+A50</f>
         <v/>
       </c>
       <c r="C50" s="19">
-        <f>IF(A50&lt;=0,0,IF(A50&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A50/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A50/$B$5-$B$16)/5)))))</f>
+        <f>IF(A50&lt;=0,0,IF(A50&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A50/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A50/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D50" s="19">
@@ -3803,17 +4224,25 @@
         <f>MIN(C50,D50)</f>
         <v/>
       </c>
+      <c r="F50" s="19">
+        <f>IF(A50&lt;=0,0,IF(A50&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A50/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A50/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G50" s="20">
+        <f>IF(F50&lt;=0,0,E50/F50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="28" t="n">
+      <c r="A51" s="29" t="n">
         <v>1.55</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="29">
         <f>$B$7+A51</f>
         <v/>
       </c>
       <c r="C51" s="19">
-        <f>IF(A51&lt;=0,0,IF(A51&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A51/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A51/$B$5-$B$16)/5)))))</f>
+        <f>IF(A51&lt;=0,0,IF(A51&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A51/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A51/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D51" s="19">
@@ -3824,17 +4253,25 @@
         <f>MIN(C51,D51)</f>
         <v/>
       </c>
+      <c r="F51" s="19">
+        <f>IF(A51&lt;=0,0,IF(A51&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A51/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A51/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G51" s="20">
+        <f>IF(F51&lt;=0,0,E51/F51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="n">
+      <c r="A52" s="29" t="n">
         <v>1.6</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="29">
         <f>$B$7+A52</f>
         <v/>
       </c>
       <c r="C52" s="19">
-        <f>IF(A52&lt;=0,0,IF(A52&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A52/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A52/$B$5-$B$16)/5)))))</f>
+        <f>IF(A52&lt;=0,0,IF(A52&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A52/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A52/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D52" s="19">
@@ -3845,17 +4282,25 @@
         <f>MIN(C52,D52)</f>
         <v/>
       </c>
+      <c r="F52" s="19">
+        <f>IF(A52&lt;=0,0,IF(A52&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A52/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A52/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G52" s="20">
+        <f>IF(F52&lt;=0,0,E52/F52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="28" t="n">
+      <c r="A53" s="29" t="n">
         <v>1.65</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="29">
         <f>$B$7+A53</f>
         <v/>
       </c>
       <c r="C53" s="19">
-        <f>IF(A53&lt;=0,0,IF(A53&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A53/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A53/$B$5-$B$16)/5)))))</f>
+        <f>IF(A53&lt;=0,0,IF(A53&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A53/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A53/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D53" s="19">
@@ -3866,17 +4311,25 @@
         <f>MIN(C53,D53)</f>
         <v/>
       </c>
+      <c r="F53" s="19">
+        <f>IF(A53&lt;=0,0,IF(A53&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A53/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A53/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G53" s="20">
+        <f>IF(F53&lt;=0,0,E53/F53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="n">
+      <c r="A54" s="29" t="n">
         <v>1.7</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="29">
         <f>$B$7+A54</f>
         <v/>
       </c>
       <c r="C54" s="19">
-        <f>IF(A54&lt;=0,0,IF(A54&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A54/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A54/$B$5-$B$16)/5)))))</f>
+        <f>IF(A54&lt;=0,0,IF(A54&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A54/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A54/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D54" s="19">
@@ -3887,17 +4340,25 @@
         <f>MIN(C54,D54)</f>
         <v/>
       </c>
+      <c r="F54" s="19">
+        <f>IF(A54&lt;=0,0,IF(A54&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A54/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A54/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G54" s="20">
+        <f>IF(F54&lt;=0,0,E54/F54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="28" t="n">
+      <c r="A55" s="29" t="n">
         <v>1.75</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="29">
         <f>$B$7+A55</f>
         <v/>
       </c>
       <c r="C55" s="19">
-        <f>IF(A55&lt;=0,0,IF(A55&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A55/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A55/$B$5-$B$16)/5)))))</f>
+        <f>IF(A55&lt;=0,0,IF(A55&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A55/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A55/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D55" s="19">
@@ -3908,17 +4369,25 @@
         <f>MIN(C55,D55)</f>
         <v/>
       </c>
+      <c r="F55" s="19">
+        <f>IF(A55&lt;=0,0,IF(A55&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A55/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A55/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G55" s="20">
+        <f>IF(F55&lt;=0,0,E55/F55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="n">
+      <c r="A56" s="29" t="n">
         <v>1.8</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="29">
         <f>$B$7+A56</f>
         <v/>
       </c>
       <c r="C56" s="19">
-        <f>IF(A56&lt;=0,0,IF(A56&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A56/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A56/$B$5-$B$16)/5)))))</f>
+        <f>IF(A56&lt;=0,0,IF(A56&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A56/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A56/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D56" s="19">
@@ -3929,17 +4398,25 @@
         <f>MIN(C56,D56)</f>
         <v/>
       </c>
+      <c r="F56" s="19">
+        <f>IF(A56&lt;=0,0,IF(A56&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A56/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A56/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G56" s="20">
+        <f>IF(F56&lt;=0,0,E56/F56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="28" t="n">
+      <c r="A57" s="29" t="n">
         <v>1.85</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="29">
         <f>$B$7+A57</f>
         <v/>
       </c>
       <c r="C57" s="19">
-        <f>IF(A57&lt;=0,0,IF(A57&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A57/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A57/$B$5-$B$16)/5)))))</f>
+        <f>IF(A57&lt;=0,0,IF(A57&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A57/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A57/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D57" s="19">
@@ -3950,17 +4427,25 @@
         <f>MIN(C57,D57)</f>
         <v/>
       </c>
+      <c r="F57" s="19">
+        <f>IF(A57&lt;=0,0,IF(A57&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A57/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A57/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G57" s="20">
+        <f>IF(F57&lt;=0,0,E57/F57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="28" t="n">
+      <c r="A58" s="29" t="n">
         <v>1.9</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="29">
         <f>$B$7+A58</f>
         <v/>
       </c>
       <c r="C58" s="19">
-        <f>IF(A58&lt;=0,0,IF(A58&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A58/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A58/$B$5-$B$16)/5)))))</f>
+        <f>IF(A58&lt;=0,0,IF(A58&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A58/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A58/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D58" s="19">
@@ -3971,17 +4456,25 @@
         <f>MIN(C58,D58)</f>
         <v/>
       </c>
+      <c r="F58" s="19">
+        <f>IF(A58&lt;=0,0,IF(A58&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A58/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A58/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G58" s="20">
+        <f>IF(F58&lt;=0,0,E58/F58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="28" t="n">
+      <c r="A59" s="29" t="n">
         <v>1.95</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="29">
         <f>$B$7+A59</f>
         <v/>
       </c>
       <c r="C59" s="19">
-        <f>IF(A59&lt;=0,0,IF(A59&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A59/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A59/$B$5-$B$16)/5)))))</f>
+        <f>IF(A59&lt;=0,0,IF(A59&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A59/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A59/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D59" s="19">
@@ -3992,17 +4485,25 @@
         <f>MIN(C59,D59)</f>
         <v/>
       </c>
+      <c r="F59" s="19">
+        <f>IF(A59&lt;=0,0,IF(A59&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A59/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A59/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G59" s="20">
+        <f>IF(F59&lt;=0,0,E59/F59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="n">
+      <c r="A60" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="29">
         <f>$B$7+A60</f>
         <v/>
       </c>
       <c r="C60" s="19">
-        <f>IF(A60&lt;=0,0,IF(A60&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A60/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A60/$B$5-$B$16)/5)))))</f>
+        <f>IF(A60&lt;=0,0,IF(A60&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A60/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A60/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D60" s="19">
@@ -4013,17 +4514,25 @@
         <f>MIN(C60,D60)</f>
         <v/>
       </c>
+      <c r="F60" s="19">
+        <f>IF(A60&lt;=0,0,IF(A60&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A60/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A60/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G60" s="20">
+        <f>IF(F60&lt;=0,0,E60/F60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="28" t="n">
+      <c r="A61" s="29" t="n">
         <v>2.05</v>
       </c>
-      <c r="B61" s="28">
+      <c r="B61" s="29">
         <f>$B$7+A61</f>
         <v/>
       </c>
       <c r="C61" s="19">
-        <f>IF(A61&lt;=0,0,IF(A61&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A61/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A61/$B$5-$B$16)/5)))))</f>
+        <f>IF(A61&lt;=0,0,IF(A61&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A61/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A61/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D61" s="19">
@@ -4034,17 +4543,25 @@
         <f>MIN(C61,D61)</f>
         <v/>
       </c>
+      <c r="F61" s="19">
+        <f>IF(A61&lt;=0,0,IF(A61&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A61/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A61/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G61" s="20">
+        <f>IF(F61&lt;=0,0,E61/F61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="28" t="n">
+      <c r="A62" s="29" t="n">
         <v>2.1</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="29">
         <f>$B$7+A62</f>
         <v/>
       </c>
       <c r="C62" s="19">
-        <f>IF(A62&lt;=0,0,IF(A62&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A62/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A62/$B$5-$B$16)/5)))))</f>
+        <f>IF(A62&lt;=0,0,IF(A62&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A62/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A62/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D62" s="19">
@@ -4055,17 +4572,25 @@
         <f>MIN(C62,D62)</f>
         <v/>
       </c>
+      <c r="F62" s="19">
+        <f>IF(A62&lt;=0,0,IF(A62&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A62/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A62/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G62" s="20">
+        <f>IF(F62&lt;=0,0,E62/F62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="28" t="n">
+      <c r="A63" s="29" t="n">
         <v>2.15</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="29">
         <f>$B$7+A63</f>
         <v/>
       </c>
       <c r="C63" s="19">
-        <f>IF(A63&lt;=0,0,IF(A63&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A63/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A63/$B$5-$B$16)/5)))))</f>
+        <f>IF(A63&lt;=0,0,IF(A63&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A63/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A63/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D63" s="19">
@@ -4076,17 +4601,25 @@
         <f>MIN(C63,D63)</f>
         <v/>
       </c>
+      <c r="F63" s="19">
+        <f>IF(A63&lt;=0,0,IF(A63&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A63/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A63/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G63" s="20">
+        <f>IF(F63&lt;=0,0,E63/F63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="28" t="n">
+      <c r="A64" s="29" t="n">
         <v>2.2</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="29">
         <f>$B$7+A64</f>
         <v/>
       </c>
       <c r="C64" s="19">
-        <f>IF(A64&lt;=0,0,IF(A64&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A64/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A64/$B$5-$B$16)/5)))))</f>
+        <f>IF(A64&lt;=0,0,IF(A64&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A64/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A64/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D64" s="19">
@@ -4097,17 +4630,25 @@
         <f>MIN(C64,D64)</f>
         <v/>
       </c>
+      <c r="F64" s="19">
+        <f>IF(A64&lt;=0,0,IF(A64&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A64/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A64/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G64" s="20">
+        <f>IF(F64&lt;=0,0,E64/F64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="28" t="n">
+      <c r="A65" s="29" t="n">
         <v>2.25</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="29">
         <f>$B$7+A65</f>
         <v/>
       </c>
       <c r="C65" s="19">
-        <f>IF(A65&lt;=0,0,IF(A65&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A65/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A65/$B$5-$B$16)/5)))))</f>
+        <f>IF(A65&lt;=0,0,IF(A65&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A65/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A65/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D65" s="19">
@@ -4118,17 +4659,25 @@
         <f>MIN(C65,D65)</f>
         <v/>
       </c>
+      <c r="F65" s="19">
+        <f>IF(A65&lt;=0,0,IF(A65&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A65/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A65/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G65" s="20">
+        <f>IF(F65&lt;=0,0,E65/F65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="28" t="n">
+      <c r="A66" s="29" t="n">
         <v>2.3</v>
       </c>
-      <c r="B66" s="28">
+      <c r="B66" s="29">
         <f>$B$7+A66</f>
         <v/>
       </c>
       <c r="C66" s="19">
-        <f>IF(A66&lt;=0,0,IF(A66&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A66/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A66/$B$5-$B$16)/5)))))</f>
+        <f>IF(A66&lt;=0,0,IF(A66&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A66/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A66/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D66" s="19">
@@ -4139,17 +4688,25 @@
         <f>MIN(C66,D66)</f>
         <v/>
       </c>
+      <c r="F66" s="19">
+        <f>IF(A66&lt;=0,0,IF(A66&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A66/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A66/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G66" s="20">
+        <f>IF(F66&lt;=0,0,E66/F66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="28" t="n">
+      <c r="A67" s="29" t="n">
         <v>2.35</v>
       </c>
-      <c r="B67" s="28">
+      <c r="B67" s="29">
         <f>$B$7+A67</f>
         <v/>
       </c>
       <c r="C67" s="19">
-        <f>IF(A67&lt;=0,0,IF(A67&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A67/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A67/$B$5-$B$16)/5)))))</f>
+        <f>IF(A67&lt;=0,0,IF(A67&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A67/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A67/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D67" s="19">
@@ -4160,17 +4717,25 @@
         <f>MIN(C67,D67)</f>
         <v/>
       </c>
+      <c r="F67" s="19">
+        <f>IF(A67&lt;=0,0,IF(A67&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A67/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A67/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G67" s="20">
+        <f>IF(F67&lt;=0,0,E67/F67)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="28" t="n">
+      <c r="A68" s="29" t="n">
         <v>2.4</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="29">
         <f>$B$7+A68</f>
         <v/>
       </c>
       <c r="C68" s="19">
-        <f>IF(A68&lt;=0,0,IF(A68&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A68/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A68/$B$5-$B$16)/5)))))</f>
+        <f>IF(A68&lt;=0,0,IF(A68&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A68/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A68/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D68" s="19">
@@ -4181,17 +4746,25 @@
         <f>MIN(C68,D68)</f>
         <v/>
       </c>
+      <c r="F68" s="19">
+        <f>IF(A68&lt;=0,0,IF(A68&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A68/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A68/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G68" s="20">
+        <f>IF(F68&lt;=0,0,E68/F68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="28" t="n">
+      <c r="A69" s="29" t="n">
         <v>2.45</v>
       </c>
-      <c r="B69" s="28">
+      <c r="B69" s="29">
         <f>$B$7+A69</f>
         <v/>
       </c>
       <c r="C69" s="19">
-        <f>IF(A69&lt;=0,0,IF(A69&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A69/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A69/$B$5-$B$16)/5)))))</f>
+        <f>IF(A69&lt;=0,0,IF(A69&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A69/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A69/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D69" s="19">
@@ -4202,17 +4775,25 @@
         <f>MIN(C69,D69)</f>
         <v/>
       </c>
+      <c r="F69" s="19">
+        <f>IF(A69&lt;=0,0,IF(A69&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A69/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A69/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G69" s="20">
+        <f>IF(F69&lt;=0,0,E69/F69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="28" t="n">
+      <c r="A70" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="29">
         <f>$B$7+A70</f>
         <v/>
       </c>
       <c r="C70" s="19">
-        <f>IF(A70&lt;=0,0,IF(A70&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A70/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A70/$B$5-$B$16)/5)))))</f>
+        <f>IF(A70&lt;=0,0,IF(A70&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A70/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A70/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D70" s="19">
@@ -4223,17 +4804,25 @@
         <f>MIN(C70,D70)</f>
         <v/>
       </c>
+      <c r="F70" s="19">
+        <f>IF(A70&lt;=0,0,IF(A70&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A70/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A70/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G70" s="20">
+        <f>IF(F70&lt;=0,0,E70/F70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="28" t="n">
+      <c r="A71" s="29" t="n">
         <v>2.55</v>
       </c>
-      <c r="B71" s="28">
+      <c r="B71" s="29">
         <f>$B$7+A71</f>
         <v/>
       </c>
       <c r="C71" s="19">
-        <f>IF(A71&lt;=0,0,IF(A71&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A71/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A71/$B$5-$B$16)/5)))))</f>
+        <f>IF(A71&lt;=0,0,IF(A71&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A71/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A71/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D71" s="19">
@@ -4244,17 +4833,25 @@
         <f>MIN(C71,D71)</f>
         <v/>
       </c>
+      <c r="F71" s="19">
+        <f>IF(A71&lt;=0,0,IF(A71&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A71/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A71/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G71" s="20">
+        <f>IF(F71&lt;=0,0,E71/F71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="28" t="n">
+      <c r="A72" s="29" t="n">
         <v>2.6</v>
       </c>
-      <c r="B72" s="28">
+      <c r="B72" s="29">
         <f>$B$7+A72</f>
         <v/>
       </c>
       <c r="C72" s="19">
-        <f>IF(A72&lt;=0,0,IF(A72&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A72/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A72/$B$5-$B$16)/5)))))</f>
+        <f>IF(A72&lt;=0,0,IF(A72&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A72/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A72/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D72" s="19">
@@ -4265,17 +4862,25 @@
         <f>MIN(C72,D72)</f>
         <v/>
       </c>
+      <c r="F72" s="19">
+        <f>IF(A72&lt;=0,0,IF(A72&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A72/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A72/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G72" s="20">
+        <f>IF(F72&lt;=0,0,E72/F72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="28" t="n">
+      <c r="A73" s="29" t="n">
         <v>2.65</v>
       </c>
-      <c r="B73" s="28">
+      <c r="B73" s="29">
         <f>$B$7+A73</f>
         <v/>
       </c>
       <c r="C73" s="19">
-        <f>IF(A73&lt;=0,0,IF(A73&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A73/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A73/$B$5-$B$16)/5)))))</f>
+        <f>IF(A73&lt;=0,0,IF(A73&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A73/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A73/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D73" s="19">
@@ -4286,17 +4891,25 @@
         <f>MIN(C73,D73)</f>
         <v/>
       </c>
+      <c r="F73" s="19">
+        <f>IF(A73&lt;=0,0,IF(A73&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A73/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A73/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G73" s="20">
+        <f>IF(F73&lt;=0,0,E73/F73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="28" t="n">
+      <c r="A74" s="29" t="n">
         <v>2.7</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="29">
         <f>$B$7+A74</f>
         <v/>
       </c>
       <c r="C74" s="19">
-        <f>IF(A74&lt;=0,0,IF(A74&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A74/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A74/$B$5-$B$16)/5)))))</f>
+        <f>IF(A74&lt;=0,0,IF(A74&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A74/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A74/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D74" s="19">
@@ -4307,17 +4920,25 @@
         <f>MIN(C74,D74)</f>
         <v/>
       </c>
+      <c r="F74" s="19">
+        <f>IF(A74&lt;=0,0,IF(A74&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A74/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A74/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G74" s="20">
+        <f>IF(F74&lt;=0,0,E74/F74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="28" t="n">
+      <c r="A75" s="29" t="n">
         <v>2.75</v>
       </c>
-      <c r="B75" s="28">
+      <c r="B75" s="29">
         <f>$B$7+A75</f>
         <v/>
       </c>
       <c r="C75" s="19">
-        <f>IF(A75&lt;=0,0,IF(A75&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A75/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A75/$B$5-$B$16)/5)))))</f>
+        <f>IF(A75&lt;=0,0,IF(A75&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A75/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A75/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D75" s="19">
@@ -4328,17 +4949,25 @@
         <f>MIN(C75,D75)</f>
         <v/>
       </c>
+      <c r="F75" s="19">
+        <f>IF(A75&lt;=0,0,IF(A75&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A75/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A75/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G75" s="20">
+        <f>IF(F75&lt;=0,0,E75/F75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="28" t="n">
+      <c r="A76" s="29" t="n">
         <v>2.8</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="29">
         <f>$B$7+A76</f>
         <v/>
       </c>
       <c r="C76" s="19">
-        <f>IF(A76&lt;=0,0,IF(A76&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A76/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A76/$B$5-$B$16)/5)))))</f>
+        <f>IF(A76&lt;=0,0,IF(A76&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A76/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A76/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D76" s="19">
@@ -4349,17 +4978,25 @@
         <f>MIN(C76,D76)</f>
         <v/>
       </c>
+      <c r="F76" s="19">
+        <f>IF(A76&lt;=0,0,IF(A76&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A76/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A76/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G76" s="20">
+        <f>IF(F76&lt;=0,0,E76/F76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="28" t="n">
+      <c r="A77" s="29" t="n">
         <v>2.85</v>
       </c>
-      <c r="B77" s="28">
+      <c r="B77" s="29">
         <f>$B$7+A77</f>
         <v/>
       </c>
       <c r="C77" s="19">
-        <f>IF(A77&lt;=0,0,IF(A77&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A77/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A77/$B$5-$B$16)/5)))))</f>
+        <f>IF(A77&lt;=0,0,IF(A77&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A77/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A77/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D77" s="19">
@@ -4370,17 +5007,25 @@
         <f>MIN(C77,D77)</f>
         <v/>
       </c>
+      <c r="F77" s="19">
+        <f>IF(A77&lt;=0,0,IF(A77&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A77/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A77/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G77" s="20">
+        <f>IF(F77&lt;=0,0,E77/F77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="28" t="n">
+      <c r="A78" s="29" t="n">
         <v>2.9</v>
       </c>
-      <c r="B78" s="28">
+      <c r="B78" s="29">
         <f>$B$7+A78</f>
         <v/>
       </c>
       <c r="C78" s="19">
-        <f>IF(A78&lt;=0,0,IF(A78&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A78/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A78/$B$5-$B$16)/5)))))</f>
+        <f>IF(A78&lt;=0,0,IF(A78&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A78/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A78/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D78" s="19">
@@ -4391,17 +5036,25 @@
         <f>MIN(C78,D78)</f>
         <v/>
       </c>
+      <c r="F78" s="19">
+        <f>IF(A78&lt;=0,0,IF(A78&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A78/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A78/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G78" s="20">
+        <f>IF(F78&lt;=0,0,E78/F78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="28" t="n">
+      <c r="A79" s="29" t="n">
         <v>2.95</v>
       </c>
-      <c r="B79" s="28">
+      <c r="B79" s="29">
         <f>$B$7+A79</f>
         <v/>
       </c>
       <c r="C79" s="19">
-        <f>IF(A79&lt;=0,0,IF(A79&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A79/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A79/$B$5-$B$16)/5)))))</f>
+        <f>IF(A79&lt;=0,0,IF(A79&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A79/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A79/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D79" s="19">
@@ -4412,17 +5065,25 @@
         <f>MIN(C79,D79)</f>
         <v/>
       </c>
+      <c r="F79" s="19">
+        <f>IF(A79&lt;=0,0,IF(A79&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A79/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A79/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G79" s="20">
+        <f>IF(F79&lt;=0,0,E79/F79)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="28" t="n">
+      <c r="A80" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B80" s="28">
+      <c r="B80" s="29">
         <f>$B$7+A80</f>
         <v/>
       </c>
       <c r="C80" s="19">
-        <f>IF(A80&lt;=0,0,IF(A80&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A80/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A80/$B$5-$B$16)/5)))))</f>
+        <f>IF(A80&lt;=0,0,IF(A80&lt;=1.2*$B$5,1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,(A80/($B$13*$B$5))^(1/$B$14)),MAX(1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*IF($B$13*$B$5&lt;=0,0,((1.2*$B$5)/($B$13*$B$5))^(1/$B$14)),1.811*(PI()*($B$5/2)^2)*SQRT($B$5)*SQRT(MAX(0,(A80/$B$5-$B$16)/7)))))</f>
         <v/>
       </c>
       <c r="D80" s="19">
@@ -4431,6 +5092,14 @@
       </c>
       <c r="E80" s="9">
         <f>MIN(C80,D80)</f>
+        <v/>
+      </c>
+      <c r="F80" s="19">
+        <f>IF(A80&lt;=0,0,IF(A80&lt;$B$5,(($B$5/2)^2/2)*((2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A80/$B$5)))))-SIN(2*ACOS(1-2*(MIN(0.999,MAX(1E-6,A80/$B$5)))))),(PI()*($B$5/2)^2)))</f>
+        <v/>
+      </c>
+      <c r="G80" s="20">
+        <f>IF(F80&lt;=0,0,E80/F80)</f>
         <v/>
       </c>
     </row>
@@ -4449,7 +5118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4472,7 +5141,7 @@
           <t>Aire (m2)</t>
         </is>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -4483,7 +5152,7 @@
           <t>Q_plein ref</t>
         </is>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4494,7 +5163,7 @@
           <t>Vmax_B (m3)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="25">
         <f>MAX(G10:G22)</f>
         <v/>
       </c>
@@ -4544,6 +5213,11 @@
       <c r="G9" s="17" t="inlineStr">
         <is>
           <t>V (m3)</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>V_Ø1200 (m/s)</t>
         </is>
       </c>
     </row>
@@ -4566,11 +5240,15 @@
         <f>MIN(B10,$B$5)</f>
         <v/>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="26" t="n">
         <v>0</v>
+      </c>
+      <c r="H10" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E10/Parametres!$C$96)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -4594,12 +5272,16 @@
         <f>IF(G10&lt;=0.01,MIN(0.5*(B10+B11),$B$5),D11)</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="21">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="26">
         <f>MAX(0,G10+(0.5*(B10+B11)-E11)*F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E11/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4624,12 +5306,16 @@
         <f>IF(G11&lt;=0.01,MIN(0.5*(B11+B12),$B$5),D12)</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="21">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="26">
         <f>MAX(0,G11+(0.5*(B11+B12)-E12)*F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E12/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4654,12 +5340,16 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$5),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="21">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E13/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4684,12 +5374,16 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$5),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="21">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="26">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E14/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4714,12 +5408,16 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$5),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="21">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="26">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E15/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4744,12 +5442,16 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$5),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="21">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E16/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4774,12 +5476,16 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$5),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="21">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E17/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4804,12 +5510,16 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$5),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="21">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="26">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E18/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4834,12 +5544,16 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$5),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="21">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="26">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E19/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4864,12 +5578,16 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$5),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="21">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="26">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E20/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4894,12 +5612,16 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$5),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="21">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="26">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E21/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4924,12 +5646,16 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$5),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="21">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="26">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,E22/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -4967,7 +5693,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>V_pas = 0.5*(A_bas+A_haut)*dWSE. Aires = somme Z1+Z2 du leve deux zones (scenario sans ponceau Ø900 intermediaire). Jaune = WSE et Surface editables (AutoCAD). Orange = 37.40 m limite ville. Ancien seuil etude 37.28 reste dans la table.</t>
         </is>
@@ -5007,197 +5733,197 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" s="29" t="n">
         <v>34.88</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Fond bassin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="n">
+      <c r="A12" s="29" t="n">
         <v>35.5</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>116</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="21">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="26">
         <f>E11+D12</f>
         <v/>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>Levé Z1+Z2 — éditer si AutoCAD diffère</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n">
+      <c r="A13" s="29" t="n">
         <v>36.01</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>429</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="21">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="26">
         <f>E12+D13</f>
         <v/>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Levé Z1+Z2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n">
+      <c r="A14" s="29" t="n">
         <v>36.5</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>530</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="21">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="26">
         <f>E13+D14</f>
         <v/>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>Levé Z1+Z2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n">
+      <c r="A15" s="29" t="n">
         <v>37</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>740</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="21">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="26">
         <f>E14+D15</f>
         <v/>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Levé Z1+Z2</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="n">
+      <c r="A16" s="32" t="n">
         <v>37.28</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>2200</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="33">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="33">
         <f>E15+D16</f>
         <v/>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>Ancien seuil étude (+1.5 m) — référence</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="32" t="n">
         <v>37.4</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>2320</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E16+D17</f>
         <v/>
       </c>
-      <c r="F17" s="33" t="inlineStr">
+      <c r="F17" s="34" t="inlineStr">
         <is>
           <t>LIMITE VILLE (WSE max + freeboard 0.6 m)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="n">
+      <c r="A18" s="29" t="n">
         <v>40</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>3732</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="21">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="26">
         <f>E17+D18</f>
         <v/>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>Sommet table</t>
         </is>
@@ -5239,7 +5965,7 @@
           <t>V @ 37.28 m (ancien seuil)</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>E16</f>
         <v/>
       </c>
@@ -5250,7 +5976,7 @@
           <t>V @ 37.40 m (limite ville)</t>
         </is>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="25">
         <f>E17</f>
         <v/>
       </c>
@@ -5275,7 +6001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5298,7 +6024,7 @@
           <t>Crest</t>
         </is>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="28">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -5309,7 +6035,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>Parametres!B28</f>
         <v/>
       </c>
@@ -5320,7 +6046,7 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>Parametres!B29</f>
         <v/>
       </c>
@@ -5331,7 +6057,7 @@
           <t>z</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>Parametres!B30</f>
         <v/>
       </c>
@@ -5342,7 +6068,7 @@
           <t>S</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>Parametres!B31</f>
         <v/>
       </c>
@@ -5353,7 +6079,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <f>Parametres!B32</f>
         <v/>
       </c>
@@ -5364,7 +6090,7 @@
           <t>Zin</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>Parametres!B13</f>
         <v/>
       </c>
@@ -5375,7 +6101,7 @@
           <t>Inclure V_ditch</t>
         </is>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <f>Parametres!B25</f>
         <v/>
       </c>
@@ -5431,16 +6157,26 @@
           <t>Qout</t>
         </is>
       </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>V_Ø1200 (m/s)</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>V_overflow (m/s)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n">
+      <c r="A13" s="29" t="n">
         <v>34.88</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>A13-$B$10</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>MAX(0,A13-$B$4)</f>
         <v/>
       </c>
@@ -5448,15 +6184,15 @@
         <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="21">
         <f>IF($B$11=1,D13*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="21">
         <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <f>F13+E13</f>
         <v/>
       </c>
@@ -5472,16 +6208,24 @@
         <f>H13+I13</f>
         <v/>
       </c>
+      <c r="K13" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H13/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L13" s="20">
+        <f>IF(D13&lt;=0,0,I13/D13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n">
+      <c r="A14" s="29" t="n">
         <v>34.98</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="29">
         <f>A14-$B$10</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>MAX(0,A14-$B$4)</f>
         <v/>
       </c>
@@ -5489,15 +6233,15 @@
         <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="21">
         <f>IF($B$11=1,D14*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="21">
         <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="26">
         <f>F14+E14</f>
         <v/>
       </c>
@@ -5513,16 +6257,24 @@
         <f>H14+I14</f>
         <v/>
       </c>
+      <c r="K14" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H14/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L14" s="20">
+        <f>IF(D14&lt;=0,0,I14/D14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n">
+      <c r="A15" s="29" t="n">
         <v>35.08</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="29">
         <f>A15-$B$10</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>MAX(0,A15-$B$4)</f>
         <v/>
       </c>
@@ -5530,15 +6282,15 @@
         <f>IF(C15&lt;=0,0,($B$5+$B$7*C15)*C15)</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="21">
         <f>IF($B$11=1,D15*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="21">
         <f>IF(A15&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A15&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1))+(A15-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="26">
         <f>F15+E15</f>
         <v/>
       </c>
@@ -5554,16 +6306,24 @@
         <f>H15+I15</f>
         <v/>
       </c>
+      <c r="K15" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H15/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L15" s="20">
+        <f>IF(D15&lt;=0,0,I15/D15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n">
+      <c r="A16" s="29" t="n">
         <v>35.18</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>A16-$B$10</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>MAX(0,A16-$B$4)</f>
         <v/>
       </c>
@@ -5571,15 +6331,15 @@
         <f>IF(C16&lt;=0,0,($B$5+$B$7*C16)*C16)</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="21">
         <f>IF($B$11=1,D16*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="21">
         <f>IF(A16&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A16&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1))+(A16-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <f>F16+E16</f>
         <v/>
       </c>
@@ -5595,16 +6355,24 @@
         <f>H16+I16</f>
         <v/>
       </c>
+      <c r="K16" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H16/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L16" s="20">
+        <f>IF(D16&lt;=0,0,I16/D16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="n">
+      <c r="A17" s="29" t="n">
         <v>35.28</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="29">
         <f>A17-$B$10</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <f>MAX(0,A17-$B$4)</f>
         <v/>
       </c>
@@ -5612,15 +6380,15 @@
         <f>IF(C17&lt;=0,0,($B$5+$B$7*C17)*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="21">
         <f>IF($B$11=1,D17*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="21">
         <f>IF(A17&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A17&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1))+(A17-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <f>F17+E17</f>
         <v/>
       </c>
@@ -5636,16 +6404,24 @@
         <f>H17+I17</f>
         <v/>
       </c>
+      <c r="K17" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H17/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L17" s="20">
+        <f>IF(D17&lt;=0,0,I17/D17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="n">
+      <c r="A18" s="29" t="n">
         <v>35.38</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>A18-$B$10</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>MAX(0,A18-$B$4)</f>
         <v/>
       </c>
@@ -5653,15 +6429,15 @@
         <f>IF(C18&lt;=0,0,($B$5+$B$7*C18)*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="21">
         <f>IF($B$11=1,D18*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="21">
         <f>IF(A18&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A18&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1))+(A18-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="26">
         <f>F18+E18</f>
         <v/>
       </c>
@@ -5677,16 +6453,24 @@
         <f>H18+I18</f>
         <v/>
       </c>
+      <c r="K18" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H18/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L18" s="20">
+        <f>IF(D18&lt;=0,0,I18/D18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="n">
+      <c r="A19" s="29" t="n">
         <v>35.48</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <f>A19-$B$10</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>MAX(0,A19-$B$4)</f>
         <v/>
       </c>
@@ -5694,15 +6478,15 @@
         <f>IF(C19&lt;=0,0,($B$5+$B$7*C19)*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="21">
         <f>IF($B$11=1,D19*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="21">
         <f>IF(A19&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A19&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1))+(A19-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="26">
         <f>F19+E19</f>
         <v/>
       </c>
@@ -5718,16 +6502,24 @@
         <f>H19+I19</f>
         <v/>
       </c>
+      <c r="K19" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H19/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L19" s="20">
+        <f>IF(D19&lt;=0,0,I19/D19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="n">
+      <c r="A20" s="29" t="n">
         <v>35.58</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="29">
         <f>A20-$B$10</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>MAX(0,A20-$B$4)</f>
         <v/>
       </c>
@@ -5735,15 +6527,15 @@
         <f>IF(C20&lt;=0,0,($B$5+$B$7*C20)*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="21">
         <f>IF($B$11=1,D20*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="21">
         <f>IF(A20&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A20&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1))+(A20-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="26">
         <f>F20+E20</f>
         <v/>
       </c>
@@ -5759,16 +6551,24 @@
         <f>H20+I20</f>
         <v/>
       </c>
+      <c r="K20" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H20/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L20" s="20">
+        <f>IF(D20&lt;=0,0,I20/D20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="n">
+      <c r="A21" s="29" t="n">
         <v>35.68</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>A21-$B$10</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>MAX(0,A21-$B$4)</f>
         <v/>
       </c>
@@ -5776,15 +6576,15 @@
         <f>IF(C21&lt;=0,0,($B$5+$B$7*C21)*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="21">
         <f>IF($B$11=1,D21*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="21">
         <f>IF(A21&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A21&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1))+(A21-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="26">
         <f>F21+E21</f>
         <v/>
       </c>
@@ -5800,16 +6600,24 @@
         <f>H21+I21</f>
         <v/>
       </c>
+      <c r="K21" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H21/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L21" s="20">
+        <f>IF(D21&lt;=0,0,I21/D21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="29" t="n">
         <v>35.78</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="29">
         <f>A22-$B$10</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <f>MAX(0,A22-$B$4)</f>
         <v/>
       </c>
@@ -5817,15 +6625,15 @@
         <f>IF(C22&lt;=0,0,($B$5+$B$7*C22)*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="21">
         <f>IF($B$11=1,D22*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="21">
         <f>IF(A22&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A22&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1))+(A22-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="26">
         <f>F22+E22</f>
         <v/>
       </c>
@@ -5841,16 +6649,24 @@
         <f>H22+I22</f>
         <v/>
       </c>
+      <c r="K22" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H22/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L22" s="20">
+        <f>IF(D22&lt;=0,0,I22/D22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="n">
+      <c r="A23" s="29" t="n">
         <v>35.88</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>A23-$B$10</f>
         <v/>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>MAX(0,A23-$B$4)</f>
         <v/>
       </c>
@@ -5858,15 +6674,15 @@
         <f>IF(C23&lt;=0,0,($B$5+$B$7*C23)*C23)</f>
         <v/>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="21">
         <f>IF($B$11=1,D23*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="21">
         <f>IF(A23&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A23&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1))+(A23-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="26">
         <f>F23+E23</f>
         <v/>
       </c>
@@ -5882,16 +6698,24 @@
         <f>H23+I23</f>
         <v/>
       </c>
+      <c r="K23" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H23/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L23" s="20">
+        <f>IF(D23&lt;=0,0,I23/D23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="n">
+      <c r="A24" s="29" t="n">
         <v>35.98</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="29">
         <f>A24-$B$10</f>
         <v/>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="29">
         <f>MAX(0,A24-$B$4)</f>
         <v/>
       </c>
@@ -5899,15 +6723,15 @@
         <f>IF(C24&lt;=0,0,($B$5+$B$7*C24)*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="21">
         <f>IF($B$11=1,D24*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="21">
         <f>IF(A24&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A24&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1))+(A24-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="26">
         <f>F24+E24</f>
         <v/>
       </c>
@@ -5923,16 +6747,24 @@
         <f>H24+I24</f>
         <v/>
       </c>
+      <c r="K24" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H24/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L24" s="20">
+        <f>IF(D24&lt;=0,0,I24/D24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="n">
+      <c r="A25" s="29" t="n">
         <v>36.08</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <f>A25-$B$10</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>MAX(0,A25-$B$4)</f>
         <v/>
       </c>
@@ -5940,15 +6772,15 @@
         <f>IF(C25&lt;=0,0,($B$5+$B$7*C25)*C25)</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="21">
         <f>IF($B$11=1,D25*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="21">
         <f>IF(A25&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A25&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1))+(A25-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="26">
         <f>F25+E25</f>
         <v/>
       </c>
@@ -5964,16 +6796,24 @@
         <f>H25+I25</f>
         <v/>
       </c>
+      <c r="K25" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H25/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L25" s="20">
+        <f>IF(D25&lt;=0,0,I25/D25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="n">
+      <c r="A26" s="29" t="n">
         <v>36.18</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="29">
         <f>A26-$B$10</f>
         <v/>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>MAX(0,A26-$B$4)</f>
         <v/>
       </c>
@@ -5981,15 +6821,15 @@
         <f>IF(C26&lt;=0,0,($B$5+$B$7*C26)*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="21">
         <f>IF($B$11=1,D26*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="21">
         <f>IF(A26&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A26&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1))+(A26-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="26">
         <f>F26+E26</f>
         <v/>
       </c>
@@ -6005,16 +6845,24 @@
         <f>H26+I26</f>
         <v/>
       </c>
+      <c r="K26" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H26/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L26" s="20">
+        <f>IF(D26&lt;=0,0,I26/D26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="n">
+      <c r="A27" s="29" t="n">
         <v>36.28</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="29">
         <f>A27-$B$10</f>
         <v/>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>MAX(0,A27-$B$4)</f>
         <v/>
       </c>
@@ -6022,15 +6870,15 @@
         <f>IF(C27&lt;=0,0,($B$5+$B$7*C27)*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="21">
         <f>IF($B$11=1,D27*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="21">
         <f>IF(A27&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A27&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1))+(A27-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="26">
         <f>F27+E27</f>
         <v/>
       </c>
@@ -6046,16 +6894,24 @@
         <f>H27+I27</f>
         <v/>
       </c>
+      <c r="K27" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H27/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L27" s="20">
+        <f>IF(D27&lt;=0,0,I27/D27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="n">
+      <c r="A28" s="29" t="n">
         <v>36.38</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="29">
         <f>A28-$B$10</f>
         <v/>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="29">
         <f>MAX(0,A28-$B$4)</f>
         <v/>
       </c>
@@ -6063,15 +6919,15 @@
         <f>IF(C28&lt;=0,0,($B$5+$B$7*C28)*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="21">
         <f>IF($B$11=1,D28*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="21">
         <f>IF(A28&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A28&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1))+(A28-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="26">
         <f>F28+E28</f>
         <v/>
       </c>
@@ -6087,16 +6943,24 @@
         <f>H28+I28</f>
         <v/>
       </c>
+      <c r="K28" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H28/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L28" s="20">
+        <f>IF(D28&lt;=0,0,I28/D28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="n">
+      <c r="A29" s="29" t="n">
         <v>36.48</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="29">
         <f>A29-$B$10</f>
         <v/>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>MAX(0,A29-$B$4)</f>
         <v/>
       </c>
@@ -6104,15 +6968,15 @@
         <f>IF(C29&lt;=0,0,($B$5+$B$7*C29)*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="21">
         <f>IF($B$11=1,D29*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="21">
         <f>IF(A29&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A29&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1))+(A29-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="26">
         <f>F29+E29</f>
         <v/>
       </c>
@@ -6128,16 +6992,24 @@
         <f>H29+I29</f>
         <v/>
       </c>
+      <c r="K29" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H29/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L29" s="20">
+        <f>IF(D29&lt;=0,0,I29/D29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="29" t="n">
         <v>36.58</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="29">
         <f>A30-$B$10</f>
         <v/>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="29">
         <f>MAX(0,A30-$B$4)</f>
         <v/>
       </c>
@@ -6145,15 +7017,15 @@
         <f>IF(C30&lt;=0,0,($B$5+$B$7*C30)*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="21">
         <f>IF($B$11=1,D30*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="21">
         <f>IF(A30&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A30&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1))+(A30-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="26">
         <f>F30+E30</f>
         <v/>
       </c>
@@ -6169,16 +7041,24 @@
         <f>H30+I30</f>
         <v/>
       </c>
+      <c r="K30" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H30/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L30" s="20">
+        <f>IF(D30&lt;=0,0,I30/D30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="29" t="n">
         <v>36.68</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="29">
         <f>A31-$B$10</f>
         <v/>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="29">
         <f>MAX(0,A31-$B$4)</f>
         <v/>
       </c>
@@ -6186,15 +7066,15 @@
         <f>IF(C31&lt;=0,0,($B$5+$B$7*C31)*C31)</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="21">
         <f>IF($B$11=1,D31*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="21">
         <f>IF(A31&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A31&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1))+(A31-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="26">
         <f>F31+E31</f>
         <v/>
       </c>
@@ -6210,16 +7090,24 @@
         <f>H31+I31</f>
         <v/>
       </c>
+      <c r="K31" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H31/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L31" s="20">
+        <f>IF(D31&lt;=0,0,I31/D31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="n">
+      <c r="A32" s="29" t="n">
         <v>36.78</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="29">
         <f>A32-$B$10</f>
         <v/>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <f>MAX(0,A32-$B$4)</f>
         <v/>
       </c>
@@ -6227,15 +7115,15 @@
         <f>IF(C32&lt;=0,0,($B$5+$B$7*C32)*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="21">
         <f>IF($B$11=1,D32*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="21">
         <f>IF(A32&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A32&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1))+(A32-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="26">
         <f>F32+E32</f>
         <v/>
       </c>
@@ -6251,16 +7139,24 @@
         <f>H32+I32</f>
         <v/>
       </c>
+      <c r="K32" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H32/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L32" s="20">
+        <f>IF(D32&lt;=0,0,I32/D32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="n">
+      <c r="A33" s="29" t="n">
         <v>36.88</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="29">
         <f>A33-$B$10</f>
         <v/>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="29">
         <f>MAX(0,A33-$B$4)</f>
         <v/>
       </c>
@@ -6268,15 +7164,15 @@
         <f>IF(C33&lt;=0,0,($B$5+$B$7*C33)*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="21">
         <f>IF($B$11=1,D33*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="21">
         <f>IF(A33&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A33&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1))+(A33-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="26">
         <f>F33+E33</f>
         <v/>
       </c>
@@ -6292,16 +7188,24 @@
         <f>H33+I33</f>
         <v/>
       </c>
+      <c r="K33" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H33/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L33" s="20">
+        <f>IF(D33&lt;=0,0,I33/D33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="n">
+      <c r="A34" s="29" t="n">
         <v>36.98</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="29">
         <f>A34-$B$10</f>
         <v/>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="29">
         <f>MAX(0,A34-$B$4)</f>
         <v/>
       </c>
@@ -6309,15 +7213,15 @@
         <f>IF(C34&lt;=0,0,($B$5+$B$7*C34)*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="21">
         <f>IF($B$11=1,D34*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="21">
         <f>IF(A34&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A34&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1))+(A34-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="26">
         <f>F34+E34</f>
         <v/>
       </c>
@@ -6333,16 +7237,24 @@
         <f>H34+I34</f>
         <v/>
       </c>
+      <c r="K34" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H34/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L34" s="20">
+        <f>IF(D34&lt;=0,0,I34/D34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="n">
+      <c r="A35" s="29" t="n">
         <v>37.08</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="29">
         <f>A35-$B$10</f>
         <v/>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="29">
         <f>MAX(0,A35-$B$4)</f>
         <v/>
       </c>
@@ -6350,15 +7262,15 @@
         <f>IF(C35&lt;=0,0,($B$5+$B$7*C35)*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="21">
         <f>IF($B$11=1,D35*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="21">
         <f>IF(A35&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A35&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1))+(A35-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="26">
         <f>F35+E35</f>
         <v/>
       </c>
@@ -6374,16 +7286,24 @@
         <f>H35+I35</f>
         <v/>
       </c>
+      <c r="K35" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H35/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L35" s="20">
+        <f>IF(D35&lt;=0,0,I35/D35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="n">
+      <c r="A36" s="29" t="n">
         <v>37.18</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="29">
         <f>A36-$B$10</f>
         <v/>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="29">
         <f>MAX(0,A36-$B$4)</f>
         <v/>
       </c>
@@ -6391,15 +7311,15 @@
         <f>IF(C36&lt;=0,0,($B$5+$B$7*C36)*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="21">
         <f>IF($B$11=1,D36*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="21">
         <f>IF(A36&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A36&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1))+(A36-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="26">
         <f>F36+E36</f>
         <v/>
       </c>
@@ -6415,16 +7335,24 @@
         <f>H36+I36</f>
         <v/>
       </c>
+      <c r="K36" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H36/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L36" s="20">
+        <f>IF(D36&lt;=0,0,I36/D36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="n">
+      <c r="A37" s="29" t="n">
         <v>37.28</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="29">
         <f>A37-$B$10</f>
         <v/>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="29">
         <f>MAX(0,A37-$B$4)</f>
         <v/>
       </c>
@@ -6432,15 +7360,15 @@
         <f>IF(C37&lt;=0,0,($B$5+$B$7*C37)*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="21">
         <f>IF($B$11=1,D37*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="21">
         <f>IF(A37&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A37&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1))+(A37-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="26">
         <f>F37+E37</f>
         <v/>
       </c>
@@ -6456,16 +7384,24 @@
         <f>H37+I37</f>
         <v/>
       </c>
+      <c r="K37" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H37/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L37" s="20">
+        <f>IF(D37&lt;=0,0,I37/D37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="n">
+      <c r="A38" s="29" t="n">
         <v>37.38</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="29">
         <f>A38-$B$10</f>
         <v/>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="29">
         <f>MAX(0,A38-$B$4)</f>
         <v/>
       </c>
@@ -6473,15 +7409,15 @@
         <f>IF(C38&lt;=0,0,($B$5+$B$7*C38)*C38)</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="21">
         <f>IF($B$11=1,D38*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="21">
         <f>IF(A38&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A38&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1))+(A38-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="26">
         <f>F38+E38</f>
         <v/>
       </c>
@@ -6497,16 +7433,24 @@
         <f>H38+I38</f>
         <v/>
       </c>
+      <c r="K38" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H38/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L38" s="20">
+        <f>IF(D38&lt;=0,0,I38/D38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="n">
+      <c r="A39" s="29" t="n">
         <v>37.48</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="29">
         <f>A39-$B$10</f>
         <v/>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="29">
         <f>MAX(0,A39-$B$4)</f>
         <v/>
       </c>
@@ -6514,15 +7458,15 @@
         <f>IF(C39&lt;=0,0,($B$5+$B$7*C39)*C39)</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="21">
         <f>IF($B$11=1,D39*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="21">
         <f>IF(A39&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A39&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1))+(A39-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="26">
         <f>F39+E39</f>
         <v/>
       </c>
@@ -6538,16 +7482,24 @@
         <f>H39+I39</f>
         <v/>
       </c>
+      <c r="K39" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H39/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L39" s="20">
+        <f>IF(D39&lt;=0,0,I39/D39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="n">
+      <c r="A40" s="29" t="n">
         <v>37.58</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="29">
         <f>A40-$B$10</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>MAX(0,A40-$B$4)</f>
         <v/>
       </c>
@@ -6555,15 +7507,15 @@
         <f>IF(C40&lt;=0,0,($B$5+$B$7*C40)*C40)</f>
         <v/>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="21">
         <f>IF($B$11=1,D40*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="21">
         <f>IF(A40&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A40&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1))+(A40-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G40" s="24">
+      <c r="G40" s="26">
         <f>F40+E40</f>
         <v/>
       </c>
@@ -6579,16 +7531,24 @@
         <f>H40+I40</f>
         <v/>
       </c>
+      <c r="K40" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H40/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L40" s="20">
+        <f>IF(D40&lt;=0,0,I40/D40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="n">
+      <c r="A41" s="29" t="n">
         <v>37.68</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="29">
         <f>A41-$B$10</f>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>MAX(0,A41-$B$4)</f>
         <v/>
       </c>
@@ -6596,15 +7556,15 @@
         <f>IF(C41&lt;=0,0,($B$5+$B$7*C41)*C41)</f>
         <v/>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="21">
         <f>IF($B$11=1,D41*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="21">
         <f>IF(A41&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A41&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1))+(A41-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="26">
         <f>F41+E41</f>
         <v/>
       </c>
@@ -6620,16 +7580,24 @@
         <f>H41+I41</f>
         <v/>
       </c>
+      <c r="K41" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H41/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L41" s="20">
+        <f>IF(D41&lt;=0,0,I41/D41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n">
+      <c r="A42" s="29" t="n">
         <v>37.78</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="29">
         <f>A42-$B$10</f>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>MAX(0,A42-$B$4)</f>
         <v/>
       </c>
@@ -6637,15 +7605,15 @@
         <f>IF(C42&lt;=0,0,($B$5+$B$7*C42)*C42)</f>
         <v/>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="21">
         <f>IF($B$11=1,D42*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="21">
         <f>IF(A42&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A42&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1))+(A42-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="26">
         <f>F42+E42</f>
         <v/>
       </c>
@@ -6661,16 +7629,24 @@
         <f>H42+I42</f>
         <v/>
       </c>
+      <c r="K42" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H42/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L42" s="20">
+        <f>IF(D42&lt;=0,0,I42/D42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="n">
+      <c r="A43" s="29" t="n">
         <v>37.88</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="29">
         <f>A43-$B$10</f>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <f>MAX(0,A43-$B$4)</f>
         <v/>
       </c>
@@ -6678,15 +7654,15 @@
         <f>IF(C43&lt;=0,0,($B$5+$B$7*C43)*C43)</f>
         <v/>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="21">
         <f>IF($B$11=1,D43*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="21">
         <f>IF(A43&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A43&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1))+(A43-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G43" s="24">
+      <c r="G43" s="26">
         <f>F43+E43</f>
         <v/>
       </c>
@@ -6702,16 +7678,24 @@
         <f>H43+I43</f>
         <v/>
       </c>
+      <c r="K43" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H43/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L43" s="20">
+        <f>IF(D43&lt;=0,0,I43/D43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="n">
+      <c r="A44" s="29" t="n">
         <v>37.98</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="29">
         <f>A44-$B$10</f>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>MAX(0,A44-$B$4)</f>
         <v/>
       </c>
@@ -6719,15 +7703,15 @@
         <f>IF(C44&lt;=0,0,($B$5+$B$7*C44)*C44)</f>
         <v/>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="21">
         <f>IF($B$11=1,D44*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="21">
         <f>IF(A44&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A44&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1))+(A44-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G44" s="24">
+      <c r="G44" s="26">
         <f>F44+E44</f>
         <v/>
       </c>
@@ -6743,16 +7727,24 @@
         <f>H44+I44</f>
         <v/>
       </c>
+      <c r="K44" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H44/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L44" s="20">
+        <f>IF(D44&lt;=0,0,I44/D44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="28" t="n">
+      <c r="A45" s="29" t="n">
         <v>38.08</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="29">
         <f>A45-$B$10</f>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>MAX(0,A45-$B$4)</f>
         <v/>
       </c>
@@ -6760,15 +7752,15 @@
         <f>IF(C45&lt;=0,0,($B$5+$B$7*C45)*C45)</f>
         <v/>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="21">
         <f>IF($B$11=1,D45*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="21">
         <f>IF(A45&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A45&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1))+(A45-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="26">
         <f>F45+E45</f>
         <v/>
       </c>
@@ -6784,16 +7776,24 @@
         <f>H45+I45</f>
         <v/>
       </c>
+      <c r="K45" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H45/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L45" s="20">
+        <f>IF(D45&lt;=0,0,I45/D45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="28" t="n">
+      <c r="A46" s="29" t="n">
         <v>38.18</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="29">
         <f>A46-$B$10</f>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="29">
         <f>MAX(0,A46-$B$4)</f>
         <v/>
       </c>
@@ -6801,15 +7801,15 @@
         <f>IF(C46&lt;=0,0,($B$5+$B$7*C46)*C46)</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="21">
         <f>IF($B$11=1,D46*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="21">
         <f>IF(A46&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A46&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1))+(A46-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G46" s="24">
+      <c r="G46" s="26">
         <f>F46+E46</f>
         <v/>
       </c>
@@ -6825,16 +7825,24 @@
         <f>H46+I46</f>
         <v/>
       </c>
+      <c r="K46" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H46/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L46" s="20">
+        <f>IF(D46&lt;=0,0,I46/D46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="28" t="n">
+      <c r="A47" s="29" t="n">
         <v>38.28</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="29">
         <f>A47-$B$10</f>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="29">
         <f>MAX(0,A47-$B$4)</f>
         <v/>
       </c>
@@ -6842,15 +7850,15 @@
         <f>IF(C47&lt;=0,0,($B$5+$B$7*C47)*C47)</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="21">
         <f>IF($B$11=1,D47*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="21">
         <f>IF(A47&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A47&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1))+(A47-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G47" s="24">
+      <c r="G47" s="26">
         <f>F47+E47</f>
         <v/>
       </c>
@@ -6866,16 +7874,24 @@
         <f>H47+I47</f>
         <v/>
       </c>
+      <c r="K47" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H47/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L47" s="20">
+        <f>IF(D47&lt;=0,0,I47/D47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="n">
+      <c r="A48" s="29" t="n">
         <v>38.38</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="29">
         <f>A48-$B$10</f>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>MAX(0,A48-$B$4)</f>
         <v/>
       </c>
@@ -6883,15 +7899,15 @@
         <f>IF(C48&lt;=0,0,($B$5+$B$7*C48)*C48)</f>
         <v/>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="21">
         <f>IF($B$11=1,D48*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="21">
         <f>IF(A48&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A48&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1))+(A48-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="26">
         <f>F48+E48</f>
         <v/>
       </c>
@@ -6907,16 +7923,24 @@
         <f>H48+I48</f>
         <v/>
       </c>
+      <c r="K48" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H48/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L48" s="20">
+        <f>IF(D48&lt;=0,0,I48/D48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="28" t="n">
+      <c r="A49" s="29" t="n">
         <v>38.48</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="29">
         <f>A49-$B$10</f>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="29">
         <f>MAX(0,A49-$B$4)</f>
         <v/>
       </c>
@@ -6924,15 +7948,15 @@
         <f>IF(C49&lt;=0,0,($B$5+$B$7*C49)*C49)</f>
         <v/>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="21">
         <f>IF($B$11=1,D49*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="21">
         <f>IF(A49&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A49&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1))+(A49-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="26">
         <f>F49+E49</f>
         <v/>
       </c>
@@ -6948,16 +7972,24 @@
         <f>H49+I49</f>
         <v/>
       </c>
+      <c r="K49" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H49/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L49" s="20">
+        <f>IF(D49&lt;=0,0,I49/D49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="n">
+      <c r="A50" s="29" t="n">
         <v>38.58</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="29">
         <f>A50-$B$10</f>
         <v/>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="29">
         <f>MAX(0,A50-$B$4)</f>
         <v/>
       </c>
@@ -6965,15 +7997,15 @@
         <f>IF(C50&lt;=0,0,($B$5+$B$7*C50)*C50)</f>
         <v/>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="21">
         <f>IF($B$11=1,D50*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="21">
         <f>IF(A50&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A50&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1))+(A50-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G50" s="24">
+      <c r="G50" s="26">
         <f>F50+E50</f>
         <v/>
       </c>
@@ -6989,16 +8021,24 @@
         <f>H50+I50</f>
         <v/>
       </c>
+      <c r="K50" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H50/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L50" s="20">
+        <f>IF(D50&lt;=0,0,I50/D50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="28" t="n">
+      <c r="A51" s="29" t="n">
         <v>38.68</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="29">
         <f>A51-$B$10</f>
         <v/>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="29">
         <f>MAX(0,A51-$B$4)</f>
         <v/>
       </c>
@@ -7006,15 +8046,15 @@
         <f>IF(C51&lt;=0,0,($B$5+$B$7*C51)*C51)</f>
         <v/>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="21">
         <f>IF($B$11=1,D51*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="21">
         <f>IF(A51&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A51&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1))+(A51-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G51" s="24">
+      <c r="G51" s="26">
         <f>F51+E51</f>
         <v/>
       </c>
@@ -7030,16 +8070,24 @@
         <f>H51+I51</f>
         <v/>
       </c>
+      <c r="K51" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H51/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L51" s="20">
+        <f>IF(D51&lt;=0,0,I51/D51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="n">
+      <c r="A52" s="29" t="n">
         <v>38.78</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="29">
         <f>A52-$B$10</f>
         <v/>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="29">
         <f>MAX(0,A52-$B$4)</f>
         <v/>
       </c>
@@ -7047,15 +8095,15 @@
         <f>IF(C52&lt;=0,0,($B$5+$B$7*C52)*C52)</f>
         <v/>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="21">
         <f>IF($B$11=1,D52*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="21">
         <f>IF(A52&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A52&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1))+(A52-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="26">
         <f>F52+E52</f>
         <v/>
       </c>
@@ -7071,16 +8119,24 @@
         <f>H52+I52</f>
         <v/>
       </c>
+      <c r="K52" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H52/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L52" s="20">
+        <f>IF(D52&lt;=0,0,I52/D52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="28" t="n">
+      <c r="A53" s="29" t="n">
         <v>38.88</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="29">
         <f>A53-$B$10</f>
         <v/>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="29">
         <f>MAX(0,A53-$B$4)</f>
         <v/>
       </c>
@@ -7088,15 +8144,15 @@
         <f>IF(C53&lt;=0,0,($B$5+$B$7*C53)*C53)</f>
         <v/>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="21">
         <f>IF($B$11=1,D53*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="21">
         <f>IF(A53&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A53&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1))+(A53-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G53" s="24">
+      <c r="G53" s="26">
         <f>F53+E53</f>
         <v/>
       </c>
@@ -7112,16 +8168,24 @@
         <f>H53+I53</f>
         <v/>
       </c>
+      <c r="K53" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H53/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L53" s="20">
+        <f>IF(D53&lt;=0,0,I53/D53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="n">
+      <c r="A54" s="29" t="n">
         <v>38.98</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="29">
         <f>A54-$B$10</f>
         <v/>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="29">
         <f>MAX(0,A54-$B$4)</f>
         <v/>
       </c>
@@ -7129,15 +8193,15 @@
         <f>IF(C54&lt;=0,0,($B$5+$B$7*C54)*C54)</f>
         <v/>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="21">
         <f>IF($B$11=1,D54*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="21">
         <f>IF(A54&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A54&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1))+(A54-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G54" s="24">
+      <c r="G54" s="26">
         <f>F54+E54</f>
         <v/>
       </c>
@@ -7153,16 +8217,24 @@
         <f>H54+I54</f>
         <v/>
       </c>
+      <c r="K54" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H54/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L54" s="20">
+        <f>IF(D54&lt;=0,0,I54/D54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="28" t="n">
+      <c r="A55" s="29" t="n">
         <v>39.08</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="29">
         <f>A55-$B$10</f>
         <v/>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="29">
         <f>MAX(0,A55-$B$4)</f>
         <v/>
       </c>
@@ -7170,15 +8242,15 @@
         <f>IF(C55&lt;=0,0,($B$5+$B$7*C55)*C55)</f>
         <v/>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="21">
         <f>IF($B$11=1,D55*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="21">
         <f>IF(A55&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A55&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1))+(A55-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G55" s="24">
+      <c r="G55" s="26">
         <f>F55+E55</f>
         <v/>
       </c>
@@ -7194,16 +8266,24 @@
         <f>H55+I55</f>
         <v/>
       </c>
+      <c r="K55" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H55/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L55" s="20">
+        <f>IF(D55&lt;=0,0,I55/D55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="n">
+      <c r="A56" s="29" t="n">
         <v>39.18</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="29">
         <f>A56-$B$10</f>
         <v/>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="29">
         <f>MAX(0,A56-$B$4)</f>
         <v/>
       </c>
@@ -7211,15 +8291,15 @@
         <f>IF(C56&lt;=0,0,($B$5+$B$7*C56)*C56)</f>
         <v/>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="21">
         <f>IF($B$11=1,D56*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F56" s="18">
+      <c r="F56" s="21">
         <f>IF(A56&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A56&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1))+(A56-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G56" s="24">
+      <c r="G56" s="26">
         <f>F56+E56</f>
         <v/>
       </c>
@@ -7235,16 +8315,24 @@
         <f>H56+I56</f>
         <v/>
       </c>
+      <c r="K56" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H56/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L56" s="20">
+        <f>IF(D56&lt;=0,0,I56/D56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="28" t="n">
+      <c r="A57" s="29" t="n">
         <v>39.28</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="29">
         <f>A57-$B$10</f>
         <v/>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="29">
         <f>MAX(0,A57-$B$4)</f>
         <v/>
       </c>
@@ -7252,15 +8340,15 @@
         <f>IF(C57&lt;=0,0,($B$5+$B$7*C57)*C57)</f>
         <v/>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="21">
         <f>IF($B$11=1,D57*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F57" s="18">
+      <c r="F57" s="21">
         <f>IF(A57&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A57&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1))+(A57-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G57" s="24">
+      <c r="G57" s="26">
         <f>F57+E57</f>
         <v/>
       </c>
@@ -7276,16 +8364,24 @@
         <f>H57+I57</f>
         <v/>
       </c>
+      <c r="K57" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H57/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L57" s="20">
+        <f>IF(D57&lt;=0,0,I57/D57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="28" t="n">
+      <c r="A58" s="29" t="n">
         <v>39.38</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="29">
         <f>A58-$B$10</f>
         <v/>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="29">
         <f>MAX(0,A58-$B$4)</f>
         <v/>
       </c>
@@ -7293,15 +8389,15 @@
         <f>IF(C58&lt;=0,0,($B$5+$B$7*C58)*C58)</f>
         <v/>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="21">
         <f>IF($B$11=1,D58*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F58" s="18">
+      <c r="F58" s="21">
         <f>IF(A58&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A58&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1))+(A58-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G58" s="24">
+      <c r="G58" s="26">
         <f>F58+E58</f>
         <v/>
       </c>
@@ -7317,16 +8413,24 @@
         <f>H58+I58</f>
         <v/>
       </c>
+      <c r="K58" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H58/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L58" s="20">
+        <f>IF(D58&lt;=0,0,I58/D58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="28" t="n">
+      <c r="A59" s="29" t="n">
         <v>39.48</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="29">
         <f>A59-$B$10</f>
         <v/>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="29">
         <f>MAX(0,A59-$B$4)</f>
         <v/>
       </c>
@@ -7334,15 +8438,15 @@
         <f>IF(C59&lt;=0,0,($B$5+$B$7*C59)*C59)</f>
         <v/>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="21">
         <f>IF($B$11=1,D59*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="21">
         <f>IF(A59&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A59&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1))+(A59-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G59" s="24">
+      <c r="G59" s="26">
         <f>F59+E59</f>
         <v/>
       </c>
@@ -7358,16 +8462,24 @@
         <f>H59+I59</f>
         <v/>
       </c>
+      <c r="K59" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H59/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L59" s="20">
+        <f>IF(D59&lt;=0,0,I59/D59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="n">
+      <c r="A60" s="29" t="n">
         <v>39.58</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="29">
         <f>A60-$B$10</f>
         <v/>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="29">
         <f>MAX(0,A60-$B$4)</f>
         <v/>
       </c>
@@ -7375,15 +8487,15 @@
         <f>IF(C60&lt;=0,0,($B$5+$B$7*C60)*C60)</f>
         <v/>
       </c>
-      <c r="E60" s="18">
+      <c r="E60" s="21">
         <f>IF($B$11=1,D60*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F60" s="18">
+      <c r="F60" s="21">
         <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G60" s="24">
+      <c r="G60" s="26">
         <f>F60+E60</f>
         <v/>
       </c>
@@ -7399,16 +8511,24 @@
         <f>H60+I60</f>
         <v/>
       </c>
+      <c r="K60" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H60/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L60" s="20">
+        <f>IF(D60&lt;=0,0,I60/D60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="28" t="n">
+      <c r="A61" s="29" t="n">
         <v>39.68</v>
       </c>
-      <c r="B61" s="28">
+      <c r="B61" s="29">
         <f>A61-$B$10</f>
         <v/>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="29">
         <f>MAX(0,A61-$B$4)</f>
         <v/>
       </c>
@@ -7416,15 +8536,15 @@
         <f>IF(C61&lt;=0,0,($B$5+$B$7*C61)*C61)</f>
         <v/>
       </c>
-      <c r="E61" s="18">
+      <c r="E61" s="21">
         <f>IF($B$11=1,D61*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F61" s="18">
+      <c r="F61" s="21">
         <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G61" s="24">
+      <c r="G61" s="26">
         <f>F61+E61</f>
         <v/>
       </c>
@@ -7440,16 +8560,24 @@
         <f>H61+I61</f>
         <v/>
       </c>
+      <c r="K61" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H61/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L61" s="20">
+        <f>IF(D61&lt;=0,0,I61/D61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="28" t="n">
+      <c r="A62" s="29" t="n">
         <v>39.78</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="29">
         <f>A62-$B$10</f>
         <v/>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="29">
         <f>MAX(0,A62-$B$4)</f>
         <v/>
       </c>
@@ -7457,15 +8585,15 @@
         <f>IF(C62&lt;=0,0,($B$5+$B$7*C62)*C62)</f>
         <v/>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="21">
         <f>IF($B$11=1,D62*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="21">
         <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G62" s="24">
+      <c r="G62" s="26">
         <f>F62+E62</f>
         <v/>
       </c>
@@ -7481,16 +8609,24 @@
         <f>H62+I62</f>
         <v/>
       </c>
+      <c r="K62" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H62/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L62" s="20">
+        <f>IF(D62&lt;=0,0,I62/D62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="28" t="n">
+      <c r="A63" s="29" t="n">
         <v>39.88</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="29">
         <f>A63-$B$10</f>
         <v/>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="29">
         <f>MAX(0,A63-$B$4)</f>
         <v/>
       </c>
@@ -7498,15 +8634,15 @@
         <f>IF(C63&lt;=0,0,($B$5+$B$7*C63)*C63)</f>
         <v/>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="21">
         <f>IF($B$11=1,D63*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="21">
         <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G63" s="24">
+      <c r="G63" s="26">
         <f>F63+E63</f>
         <v/>
       </c>
@@ -7522,16 +8658,24 @@
         <f>H63+I63</f>
         <v/>
       </c>
+      <c r="K63" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H63/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L63" s="20">
+        <f>IF(D63&lt;=0,0,I63/D63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="28" t="n">
+      <c r="A64" s="29" t="n">
         <v>39.98</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="29">
         <f>A64-$B$10</f>
         <v/>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="29">
         <f>MAX(0,A64-$B$4)</f>
         <v/>
       </c>
@@ -7539,15 +8683,15 @@
         <f>IF(C64&lt;=0,0,($B$5+$B$7*C64)*C64)</f>
         <v/>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="21">
         <f>IF($B$11=1,D64*$B$9,0)</f>
         <v/>
       </c>
-      <c r="F64" s="18">
+      <c r="F64" s="21">
         <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G64" s="24">
+      <c r="G64" s="26">
         <f>F64+E64</f>
         <v/>
       </c>
@@ -7561,6 +8705,14 @@
       </c>
       <c r="J64" s="9">
         <f>H64+I64</f>
+        <v/>
+      </c>
+      <c r="K64" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,H64/Parametres!$C$96)</f>
+        <v/>
+      </c>
+      <c r="L64" s="20">
+        <f>IF(D64&lt;=0,0,I64/D64)</f>
         <v/>
       </c>
     </row>
@@ -7579,7 +8731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7602,7 +8754,7 @@
           <t>Q_plein ref</t>
         </is>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -7613,7 +8765,7 @@
           <t>Crest</t>
         </is>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -7624,7 +8776,7 @@
           <t>Vmax_C</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="25">
         <f>MAX(F10:F22)</f>
         <v/>
       </c>
@@ -7674,6 +8826,11 @@
       <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Overflow?</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>V_eq_Ø1200 (m/s)</t>
         </is>
       </c>
     </row>
@@ -7694,16 +8851,20 @@
         <f>MIN(B10,$B$4)</f>
         <v/>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
+      </c>
+      <c r="H10" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D10/Parametres!$C$96)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -7723,16 +8884,20 @@
         <f>IF(F10&lt;=0.01,MIN(0.5*(B10+B11),$B$4),IF(C11&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C11&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C11,Compose_1200!$A$13:$A$64,1))+(C11-INDEX(Compose_1200!$A$13:$A$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C11,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C11,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="21">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="26">
         <f>MAX(0,F10+(0.5*(B10+B11)-D11)*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="18">
         <f>IF(C11&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H11" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D11/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7753,16 +8918,20 @@
         <f>IF(F11&lt;=0.01,MIN(0.5*(B11+B12),$B$4),IF(C12&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C12&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C12,Compose_1200!$A$13:$A$64,1))+(C12-INDEX(Compose_1200!$A$13:$A$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C12,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C12,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="21">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="26">
         <f>MAX(0,F11+(0.5*(B11+B12)-D12)*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="18">
         <f>IF(C12&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H12" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D12/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7783,16 +8952,20 @@
         <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$4),IF(C13&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C13&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C13,Compose_1200!$A$13:$A$64,1))+(C13-INDEX(Compose_1200!$A$13:$A$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C13,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C13,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="21">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="18">
         <f>IF(C13&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H13" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D13/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7813,16 +8986,20 @@
         <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$4),IF(C14&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C14&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C14,Compose_1200!$A$13:$A$64,1))+(C14-INDEX(Compose_1200!$A$13:$A$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C14,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C14,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="21">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="26">
         <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="18">
         <f>IF(C14&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H14" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D14/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7843,16 +9020,20 @@
         <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$4),IF(C15&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C15&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C15,Compose_1200!$A$13:$A$64,1))+(C15-INDEX(Compose_1200!$A$13:$A$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C15,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C15,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="21">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="26">
         <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="18">
         <f>IF(C15&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H15" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D15/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7873,16 +9054,20 @@
         <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C16,Compose_1200!$A$13:$A$64,1))+(C16-INDEX(Compose_1200!$A$13:$A$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C16,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C16,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="21">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="26">
         <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="18">
         <f>IF(C16&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H16" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D16/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7903,16 +9088,20 @@
         <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C17,Compose_1200!$A$13:$A$64,1))+(C17-INDEX(Compose_1200!$A$13:$A$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C17,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C17,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="21">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="26">
         <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="18">
         <f>IF(C17&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H17" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D17/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7933,16 +9122,20 @@
         <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C18,Compose_1200!$A$13:$A$64,1))+(C18-INDEX(Compose_1200!$A$13:$A$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C18,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C18,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="21">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="26">
         <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="18">
         <f>IF(C18&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H18" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D18/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7963,16 +9156,20 @@
         <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C19,Compose_1200!$A$13:$A$64,1))+(C19-INDEX(Compose_1200!$A$13:$A$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C19,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C19,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="21">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="26">
         <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="18">
         <f>IF(C19&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D19/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7993,16 +9190,20 @@
         <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C20,Compose_1200!$A$13:$A$64,1))+(C20-INDEX(Compose_1200!$A$13:$A$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C20,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C20,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="21">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="26">
         <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="18">
         <f>IF(C20&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D20/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8023,16 +9224,20 @@
         <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C21,Compose_1200!$A$13:$A$64,1))+(C21-INDEX(Compose_1200!$A$13:$A$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C21,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C21,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="21">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="26">
         <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="18">
         <f>IF(C21&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H21" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D21/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8053,16 +9258,20 @@
         <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_1200!$A$13:$A$64,1),INDEX(Compose_1200!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_1200!$A$13:$A$64,ROWS(Compose_1200!$A$13:$A$64)),INDEX(Compose_1200!$J$13:$J$64,ROWS(Compose_1200!$J$13:$J$64)),INDEX(Compose_1200!$J$13:$J$64,MATCH(C22,Compose_1200!$A$13:$A$64,1))+(C22-INDEX(Compose_1200!$A$13:$A$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)))/(INDEX(Compose_1200!$A$13:$A$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$A$13:$A$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)))*(INDEX(Compose_1200!$J$13:$J$64,MATCH(C22,Compose_1200!$A$13:$A$64,1)+1)-INDEX(Compose_1200!$J$13:$J$64,MATCH(C22,Compose_1200!$A$13:$A$64,1))))))</f>
         <v/>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="21">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="26">
         <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="18">
         <f>IF(C22&gt;$B$5,"oui","non")</f>
+        <v/>
+      </c>
+      <c r="H22" s="20">
+        <f>IF(Parametres!$C$96&lt;=0,0,D22/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8088,7 +9297,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Methode — retention SANS Ø900</t>
         </is>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
@@ -6213,7 +6213,7 @@
         <v/>
       </c>
       <c r="L13" s="20">
-        <f>IF(D13&lt;=0,0,I13/D13)</f>
+        <f>IF(OR(C13&lt;0.05,D13&lt;0.05),"",I13/D13)</f>
         <v/>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="L14" s="20">
-        <f>IF(D14&lt;=0,0,I14/D14)</f>
+        <f>IF(OR(C14&lt;0.05,D14&lt;0.05),"",I14/D14)</f>
         <v/>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
         <v/>
       </c>
       <c r="L15" s="20">
-        <f>IF(D15&lt;=0,0,I15/D15)</f>
+        <f>IF(OR(C15&lt;0.05,D15&lt;0.05),"",I15/D15)</f>
         <v/>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
         <v/>
       </c>
       <c r="L16" s="20">
-        <f>IF(D16&lt;=0,0,I16/D16)</f>
+        <f>IF(OR(C16&lt;0.05,D16&lt;0.05),"",I16/D16)</f>
         <v/>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
         <v/>
       </c>
       <c r="L17" s="20">
-        <f>IF(D17&lt;=0,0,I17/D17)</f>
+        <f>IF(OR(C17&lt;0.05,D17&lt;0.05),"",I17/D17)</f>
         <v/>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
         <v/>
       </c>
       <c r="L18" s="20">
-        <f>IF(D18&lt;=0,0,I18/D18)</f>
+        <f>IF(OR(C18&lt;0.05,D18&lt;0.05),"",I18/D18)</f>
         <v/>
       </c>
     </row>
@@ -6507,7 +6507,7 @@
         <v/>
       </c>
       <c r="L19" s="20">
-        <f>IF(D19&lt;=0,0,I19/D19)</f>
+        <f>IF(OR(C19&lt;0.05,D19&lt;0.05),"",I19/D19)</f>
         <v/>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
         <v/>
       </c>
       <c r="L20" s="20">
-        <f>IF(D20&lt;=0,0,I20/D20)</f>
+        <f>IF(OR(C20&lt;0.05,D20&lt;0.05),"",I20/D20)</f>
         <v/>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
         <v/>
       </c>
       <c r="L21" s="20">
-        <f>IF(D21&lt;=0,0,I21/D21)</f>
+        <f>IF(OR(C21&lt;0.05,D21&lt;0.05),"",I21/D21)</f>
         <v/>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
         <v/>
       </c>
       <c r="L22" s="20">
-        <f>IF(D22&lt;=0,0,I22/D22)</f>
+        <f>IF(OR(C22&lt;0.05,D22&lt;0.05),"",I22/D22)</f>
         <v/>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
         <v/>
       </c>
       <c r="L23" s="20">
-        <f>IF(D23&lt;=0,0,I23/D23)</f>
+        <f>IF(OR(C23&lt;0.05,D23&lt;0.05),"",I23/D23)</f>
         <v/>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
         <v/>
       </c>
       <c r="L24" s="20">
-        <f>IF(D24&lt;=0,0,I24/D24)</f>
+        <f>IF(OR(C24&lt;0.05,D24&lt;0.05),"",I24/D24)</f>
         <v/>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
         <v/>
       </c>
       <c r="L25" s="20">
-        <f>IF(D25&lt;=0,0,I25/D25)</f>
+        <f>IF(OR(C25&lt;0.05,D25&lt;0.05),"",I25/D25)</f>
         <v/>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
         <v/>
       </c>
       <c r="L26" s="20">
-        <f>IF(D26&lt;=0,0,I26/D26)</f>
+        <f>IF(OR(C26&lt;0.05,D26&lt;0.05),"",I26/D26)</f>
         <v/>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
         <v/>
       </c>
       <c r="L27" s="20">
-        <f>IF(D27&lt;=0,0,I27/D27)</f>
+        <f>IF(OR(C27&lt;0.05,D27&lt;0.05),"",I27/D27)</f>
         <v/>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
         <v/>
       </c>
       <c r="L28" s="20">
-        <f>IF(D28&lt;=0,0,I28/D28)</f>
+        <f>IF(OR(C28&lt;0.05,D28&lt;0.05),"",I28/D28)</f>
         <v/>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
         <v/>
       </c>
       <c r="L29" s="20">
-        <f>IF(D29&lt;=0,0,I29/D29)</f>
+        <f>IF(OR(C29&lt;0.05,D29&lt;0.05),"",I29/D29)</f>
         <v/>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
         <v/>
       </c>
       <c r="L30" s="20">
-        <f>IF(D30&lt;=0,0,I30/D30)</f>
+        <f>IF(OR(C30&lt;0.05,D30&lt;0.05),"",I30/D30)</f>
         <v/>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
         <v/>
       </c>
       <c r="L31" s="20">
-        <f>IF(D31&lt;=0,0,I31/D31)</f>
+        <f>IF(OR(C31&lt;0.05,D31&lt;0.05),"",I31/D31)</f>
         <v/>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
         <v/>
       </c>
       <c r="L32" s="20">
-        <f>IF(D32&lt;=0,0,I32/D32)</f>
+        <f>IF(OR(C32&lt;0.05,D32&lt;0.05),"",I32/D32)</f>
         <v/>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
         <v/>
       </c>
       <c r="L33" s="20">
-        <f>IF(D33&lt;=0,0,I33/D33)</f>
+        <f>IF(OR(C33&lt;0.05,D33&lt;0.05),"",I33/D33)</f>
         <v/>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
         <v/>
       </c>
       <c r="L34" s="20">
-        <f>IF(D34&lt;=0,0,I34/D34)</f>
+        <f>IF(OR(C34&lt;0.05,D34&lt;0.05),"",I34/D34)</f>
         <v/>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         <v/>
       </c>
       <c r="L35" s="20">
-        <f>IF(D35&lt;=0,0,I35/D35)</f>
+        <f>IF(OR(C35&lt;0.05,D35&lt;0.05),"",I35/D35)</f>
         <v/>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
         <v/>
       </c>
       <c r="L36" s="20">
-        <f>IF(D36&lt;=0,0,I36/D36)</f>
+        <f>IF(OR(C36&lt;0.05,D36&lt;0.05),"",I36/D36)</f>
         <v/>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
         <v/>
       </c>
       <c r="L37" s="20">
-        <f>IF(D37&lt;=0,0,I37/D37)</f>
+        <f>IF(OR(C37&lt;0.05,D37&lt;0.05),"",I37/D37)</f>
         <v/>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
         <v/>
       </c>
       <c r="L38" s="20">
-        <f>IF(D38&lt;=0,0,I38/D38)</f>
+        <f>IF(OR(C38&lt;0.05,D38&lt;0.05),"",I38/D38)</f>
         <v/>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
         <v/>
       </c>
       <c r="L39" s="20">
-        <f>IF(D39&lt;=0,0,I39/D39)</f>
+        <f>IF(OR(C39&lt;0.05,D39&lt;0.05),"",I39/D39)</f>
         <v/>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
         <v/>
       </c>
       <c r="L40" s="20">
-        <f>IF(D40&lt;=0,0,I40/D40)</f>
+        <f>IF(OR(C40&lt;0.05,D40&lt;0.05),"",I40/D40)</f>
         <v/>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
         <v/>
       </c>
       <c r="L41" s="20">
-        <f>IF(D41&lt;=0,0,I41/D41)</f>
+        <f>IF(OR(C41&lt;0.05,D41&lt;0.05),"",I41/D41)</f>
         <v/>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
         <v/>
       </c>
       <c r="L42" s="20">
-        <f>IF(D42&lt;=0,0,I42/D42)</f>
+        <f>IF(OR(C42&lt;0.05,D42&lt;0.05),"",I42/D42)</f>
         <v/>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
         <v/>
       </c>
       <c r="L43" s="20">
-        <f>IF(D43&lt;=0,0,I43/D43)</f>
+        <f>IF(OR(C43&lt;0.05,D43&lt;0.05),"",I43/D43)</f>
         <v/>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
         <v/>
       </c>
       <c r="L44" s="20">
-        <f>IF(D44&lt;=0,0,I44/D44)</f>
+        <f>IF(OR(C44&lt;0.05,D44&lt;0.05),"",I44/D44)</f>
         <v/>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
         <v/>
       </c>
       <c r="L45" s="20">
-        <f>IF(D45&lt;=0,0,I45/D45)</f>
+        <f>IF(OR(C45&lt;0.05,D45&lt;0.05),"",I45/D45)</f>
         <v/>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="L46" s="20">
-        <f>IF(D46&lt;=0,0,I46/D46)</f>
+        <f>IF(OR(C46&lt;0.05,D46&lt;0.05),"",I46/D46)</f>
         <v/>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
         <v/>
       </c>
       <c r="L47" s="20">
-        <f>IF(D47&lt;=0,0,I47/D47)</f>
+        <f>IF(OR(C47&lt;0.05,D47&lt;0.05),"",I47/D47)</f>
         <v/>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
         <v/>
       </c>
       <c r="L48" s="20">
-        <f>IF(D48&lt;=0,0,I48/D48)</f>
+        <f>IF(OR(C48&lt;0.05,D48&lt;0.05),"",I48/D48)</f>
         <v/>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
         <v/>
       </c>
       <c r="L49" s="20">
-        <f>IF(D49&lt;=0,0,I49/D49)</f>
+        <f>IF(OR(C49&lt;0.05,D49&lt;0.05),"",I49/D49)</f>
         <v/>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
         <v/>
       </c>
       <c r="L50" s="20">
-        <f>IF(D50&lt;=0,0,I50/D50)</f>
+        <f>IF(OR(C50&lt;0.05,D50&lt;0.05),"",I50/D50)</f>
         <v/>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
         <v/>
       </c>
       <c r="L51" s="20">
-        <f>IF(D51&lt;=0,0,I51/D51)</f>
+        <f>IF(OR(C51&lt;0.05,D51&lt;0.05),"",I51/D51)</f>
         <v/>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
         <v/>
       </c>
       <c r="L52" s="20">
-        <f>IF(D52&lt;=0,0,I52/D52)</f>
+        <f>IF(OR(C52&lt;0.05,D52&lt;0.05),"",I52/D52)</f>
         <v/>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
         <v/>
       </c>
       <c r="L53" s="20">
-        <f>IF(D53&lt;=0,0,I53/D53)</f>
+        <f>IF(OR(C53&lt;0.05,D53&lt;0.05),"",I53/D53)</f>
         <v/>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
         <v/>
       </c>
       <c r="L54" s="20">
-        <f>IF(D54&lt;=0,0,I54/D54)</f>
+        <f>IF(OR(C54&lt;0.05,D54&lt;0.05),"",I54/D54)</f>
         <v/>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
         <v/>
       </c>
       <c r="L55" s="20">
-        <f>IF(D55&lt;=0,0,I55/D55)</f>
+        <f>IF(OR(C55&lt;0.05,D55&lt;0.05),"",I55/D55)</f>
         <v/>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
         <v/>
       </c>
       <c r="L56" s="20">
-        <f>IF(D56&lt;=0,0,I56/D56)</f>
+        <f>IF(OR(C56&lt;0.05,D56&lt;0.05),"",I56/D56)</f>
         <v/>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
         <v/>
       </c>
       <c r="L57" s="20">
-        <f>IF(D57&lt;=0,0,I57/D57)</f>
+        <f>IF(OR(C57&lt;0.05,D57&lt;0.05),"",I57/D57)</f>
         <v/>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
         <v/>
       </c>
       <c r="L58" s="20">
-        <f>IF(D58&lt;=0,0,I58/D58)</f>
+        <f>IF(OR(C58&lt;0.05,D58&lt;0.05),"",I58/D58)</f>
         <v/>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
         <v/>
       </c>
       <c r="L59" s="20">
-        <f>IF(D59&lt;=0,0,I59/D59)</f>
+        <f>IF(OR(C59&lt;0.05,D59&lt;0.05),"",I59/D59)</f>
         <v/>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
         <v/>
       </c>
       <c r="L60" s="20">
-        <f>IF(D60&lt;=0,0,I60/D60)</f>
+        <f>IF(OR(C60&lt;0.05,D60&lt;0.05),"",I60/D60)</f>
         <v/>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
         <v/>
       </c>
       <c r="L61" s="20">
-        <f>IF(D61&lt;=0,0,I61/D61)</f>
+        <f>IF(OR(C61&lt;0.05,D61&lt;0.05),"",I61/D61)</f>
         <v/>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
         <v/>
       </c>
       <c r="L62" s="20">
-        <f>IF(D62&lt;=0,0,I62/D62)</f>
+        <f>IF(OR(C62&lt;0.05,D62&lt;0.05),"",I62/D62)</f>
         <v/>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
         <v/>
       </c>
       <c r="L63" s="20">
-        <f>IF(D63&lt;=0,0,I63/D63)</f>
+        <f>IF(OR(C63&lt;0.05,D63&lt;0.05),"",I63/D63)</f>
         <v/>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
         <v/>
       </c>
       <c r="L64" s="20">
-        <f>IF(D64&lt;=0,0,I64/D64)</f>
+        <f>IF(OR(C64&lt;0.05,D64&lt;0.05),"",I64/D64)</f>
         <v/>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>V_eq_Ø1200 (m/s)</t>
+          <t>V_pipe_seul (m/s)</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="H10" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D10/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C10&gt;$B$5),"",D10/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D11/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C11&gt;$B$5),"",D11/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D12/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C12&gt;$B$5),"",D12/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D13/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C13&gt;$B$5),"",D13/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
         <v/>
       </c>
       <c r="H14" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D14/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C14&gt;$B$5),"",D14/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D15/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C15&gt;$B$5),"",D15/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D16/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C16&gt;$B$5),"",D16/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D17/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C17&gt;$B$5),"",D17/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
         <v/>
       </c>
       <c r="H18" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D18/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C18&gt;$B$5),"",D18/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D19/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C19&gt;$B$5),"",D19/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D20/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C20&gt;$B$5),"",D20/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
         <v/>
       </c>
       <c r="H21" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D21/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C21&gt;$B$5),"",D21/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,D22/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$96&lt;=0,C22&gt;$B$5),"",D22/Parametres!$C$96)</f>
         <v/>
       </c>
     </row>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Sans_900.xlsx
@@ -1683,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2212,115 +2212,115 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="16" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>Vitesses de reference — V = Q / A_plein</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Sans Ø900: control = Ø1200. V_eq = Q/A_plein. Partiellement rempli: V reelle = Q/A(h) plus elevee — voir Courbe_QH_1200.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Ouvrage</t>
         </is>
       </c>
-      <c r="B94" s="17" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>D (m)</t>
         </is>
       </c>
-      <c r="C94" s="17" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>A_plein (m2)</t>
         </is>
       </c>
-      <c r="D94" s="17" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Q ref</t>
         </is>
       </c>
-      <c r="E94" s="17" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>V_eq (m/s)</t>
         </is>
       </c>
-      <c r="F94" s="17" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="18" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>Ø1500 (entree)</t>
         </is>
       </c>
-      <c r="B95" s="18" t="n">
+      <c r="B63" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="C95" s="19">
-        <f>PI()*B95^2/4</f>
-        <v/>
-      </c>
-      <c r="D95" s="19">
+      <c r="C63" s="19">
+        <f>PI()*B63^2/4</f>
+        <v/>
+      </c>
+      <c r="D63" s="19">
         <f>Hydrogramme!B4</f>
         <v/>
       </c>
-      <c r="E95" s="20">
-        <f>IF(C95&lt;=0,0,D95/C95)</f>
-        <v/>
-      </c>
-      <c r="F95" s="18" t="inlineStr">
+      <c r="E63" s="20">
+        <f>IF(C63&lt;=0,0,D63/C63)</f>
+        <v/>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
         <is>
           <t>Qpointe</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="18" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t>Ø1200 (controle)</t>
         </is>
       </c>
-      <c r="B96" s="18">
+      <c r="B64" s="18">
         <f>B11</f>
         <v/>
       </c>
-      <c r="C96" s="19">
+      <c r="C64" s="19">
         <f>B16</f>
         <v/>
       </c>
-      <c r="D96" s="19">
+      <c r="D64" s="19">
         <f>B18</f>
         <v/>
       </c>
-      <c r="E96" s="20">
-        <f>IF(C96&lt;=0,0,D96/C96)</f>
-        <v/>
-      </c>
-      <c r="F96" s="18" t="inlineStr">
+      <c r="E64" s="20">
+        <f>IF(C64&lt;=0,0,D64/C64)</f>
+        <v/>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
         <is>
           <t>Q_plein Manning</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>V_Ø1200 @ Qout Calcul_A (m/s)</t>
         </is>
       </c>
-      <c r="B97" s="14">
-        <f>IF(C96&lt;=0,0,Calcul_A!B2/C96)</f>
+      <c r="B65" s="14">
+        <f>IF(C64&lt;=0,0,Calcul_A!B2/C64)</f>
         <v/>
       </c>
     </row>
@@ -2328,8 +2328,8 @@
   <mergeCells count="8">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A2:F3"/>
-    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A55:F55"/>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C8/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C8/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         <v/>
       </c>
       <c r="F9" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C9/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C9/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C10/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C10/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         <v/>
       </c>
       <c r="F11" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C11/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C11/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
         <v/>
       </c>
       <c r="F12" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C12/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C12/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C13/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C13/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
         <v/>
       </c>
       <c r="F14" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C14/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C14/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C15/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C15/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C16/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C16/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C17/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C17/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
         <v/>
       </c>
       <c r="F18" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C18/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C18/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
         <v/>
       </c>
       <c r="F19" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C19/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C19/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
       <c r="F20" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,C20/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,C20/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E10/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E10/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E11/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E11/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E12/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E12/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E13/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E13/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
         <v/>
       </c>
       <c r="H14" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E14/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E14/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E15/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E15/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E16/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E16/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E17/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E17/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
         <v/>
       </c>
       <c r="H18" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E18/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E18/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E19/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E19/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E20/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E20/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="H21" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E21/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E21/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,E22/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,E22/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="K13" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H13/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H13/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L13" s="20">
@@ -6258,7 +6258,7 @@
         <v/>
       </c>
       <c r="K14" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H14/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H14/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L14" s="20">
@@ -6307,7 +6307,7 @@
         <v/>
       </c>
       <c r="K15" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H15/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H15/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L15" s="20">
@@ -6356,7 +6356,7 @@
         <v/>
       </c>
       <c r="K16" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H16/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H16/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L16" s="20">
@@ -6405,7 +6405,7 @@
         <v/>
       </c>
       <c r="K17" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H17/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H17/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L17" s="20">
@@ -6454,7 +6454,7 @@
         <v/>
       </c>
       <c r="K18" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H18/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H18/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L18" s="20">
@@ -6503,7 +6503,7 @@
         <v/>
       </c>
       <c r="K19" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H19/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H19/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L19" s="20">
@@ -6552,7 +6552,7 @@
         <v/>
       </c>
       <c r="K20" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H20/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H20/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L20" s="20">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="K21" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H21/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H21/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L21" s="20">
@@ -6650,7 +6650,7 @@
         <v/>
       </c>
       <c r="K22" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H22/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H22/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L22" s="20">
@@ -6699,7 +6699,7 @@
         <v/>
       </c>
       <c r="K23" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H23/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H23/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L23" s="20">
@@ -6748,7 +6748,7 @@
         <v/>
       </c>
       <c r="K24" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H24/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H24/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L24" s="20">
@@ -6797,7 +6797,7 @@
         <v/>
       </c>
       <c r="K25" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H25/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H25/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L25" s="20">
@@ -6846,7 +6846,7 @@
         <v/>
       </c>
       <c r="K26" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H26/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H26/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L26" s="20">
@@ -6895,7 +6895,7 @@
         <v/>
       </c>
       <c r="K27" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H27/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H27/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L27" s="20">
@@ -6944,7 +6944,7 @@
         <v/>
       </c>
       <c r="K28" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H28/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H28/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L28" s="20">
@@ -6993,7 +6993,7 @@
         <v/>
       </c>
       <c r="K29" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H29/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H29/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L29" s="20">
@@ -7042,7 +7042,7 @@
         <v/>
       </c>
       <c r="K30" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H30/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H30/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L30" s="20">
@@ -7091,7 +7091,7 @@
         <v/>
       </c>
       <c r="K31" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H31/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H31/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L31" s="20">
@@ -7140,7 +7140,7 @@
         <v/>
       </c>
       <c r="K32" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H32/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H32/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L32" s="20">
@@ -7189,7 +7189,7 @@
         <v/>
       </c>
       <c r="K33" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H33/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H33/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L33" s="20">
@@ -7238,7 +7238,7 @@
         <v/>
       </c>
       <c r="K34" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H34/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H34/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L34" s="20">
@@ -7287,7 +7287,7 @@
         <v/>
       </c>
       <c r="K35" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H35/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H35/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L35" s="20">
@@ -7336,7 +7336,7 @@
         <v/>
       </c>
       <c r="K36" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H36/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H36/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L36" s="20">
@@ -7385,7 +7385,7 @@
         <v/>
       </c>
       <c r="K37" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H37/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H37/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L37" s="20">
@@ -7434,7 +7434,7 @@
         <v/>
       </c>
       <c r="K38" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H38/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H38/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L38" s="20">
@@ -7483,7 +7483,7 @@
         <v/>
       </c>
       <c r="K39" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H39/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H39/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L39" s="20">
@@ -7532,7 +7532,7 @@
         <v/>
       </c>
       <c r="K40" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H40/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H40/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L40" s="20">
@@ -7581,7 +7581,7 @@
         <v/>
       </c>
       <c r="K41" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H41/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H41/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L41" s="20">
@@ -7630,7 +7630,7 @@
         <v/>
       </c>
       <c r="K42" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H42/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H42/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L42" s="20">
@@ -7679,7 +7679,7 @@
         <v/>
       </c>
       <c r="K43" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H43/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H43/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L43" s="20">
@@ -7728,7 +7728,7 @@
         <v/>
       </c>
       <c r="K44" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H44/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H44/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L44" s="20">
@@ -7777,7 +7777,7 @@
         <v/>
       </c>
       <c r="K45" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H45/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H45/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L45" s="20">
@@ -7826,7 +7826,7 @@
         <v/>
       </c>
       <c r="K46" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H46/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H46/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L46" s="20">
@@ -7875,7 +7875,7 @@
         <v/>
       </c>
       <c r="K47" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H47/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H47/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L47" s="20">
@@ -7924,7 +7924,7 @@
         <v/>
       </c>
       <c r="K48" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H48/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H48/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L48" s="20">
@@ -7973,7 +7973,7 @@
         <v/>
       </c>
       <c r="K49" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H49/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H49/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L49" s="20">
@@ -8022,7 +8022,7 @@
         <v/>
       </c>
       <c r="K50" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H50/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H50/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L50" s="20">
@@ -8071,7 +8071,7 @@
         <v/>
       </c>
       <c r="K51" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H51/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H51/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L51" s="20">
@@ -8120,7 +8120,7 @@
         <v/>
       </c>
       <c r="K52" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H52/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H52/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L52" s="20">
@@ -8169,7 +8169,7 @@
         <v/>
       </c>
       <c r="K53" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H53/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H53/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L53" s="20">
@@ -8218,7 +8218,7 @@
         <v/>
       </c>
       <c r="K54" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H54/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H54/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L54" s="20">
@@ -8267,7 +8267,7 @@
         <v/>
       </c>
       <c r="K55" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H55/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H55/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L55" s="20">
@@ -8316,7 +8316,7 @@
         <v/>
       </c>
       <c r="K56" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H56/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H56/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L56" s="20">
@@ -8365,7 +8365,7 @@
         <v/>
       </c>
       <c r="K57" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H57/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H57/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L57" s="20">
@@ -8414,7 +8414,7 @@
         <v/>
       </c>
       <c r="K58" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H58/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H58/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L58" s="20">
@@ -8463,7 +8463,7 @@
         <v/>
       </c>
       <c r="K59" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H59/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H59/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L59" s="20">
@@ -8512,7 +8512,7 @@
         <v/>
       </c>
       <c r="K60" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H60/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H60/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L60" s="20">
@@ -8561,7 +8561,7 @@
         <v/>
       </c>
       <c r="K61" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H61/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H61/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L61" s="20">
@@ -8610,7 +8610,7 @@
         <v/>
       </c>
       <c r="K62" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H62/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H62/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L62" s="20">
@@ -8659,7 +8659,7 @@
         <v/>
       </c>
       <c r="K63" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H63/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H63/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L63" s="20">
@@ -8708,7 +8708,7 @@
         <v/>
       </c>
       <c r="K64" s="20">
-        <f>IF(Parametres!$C$96&lt;=0,0,H64/Parametres!$C$96)</f>
+        <f>IF(Parametres!$C$64&lt;=0,0,H64/Parametres!$C$64)</f>
         <v/>
       </c>
       <c r="L64" s="20">
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="H10" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C10&gt;$B$5),"",D10/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C10&gt;$B$5),"",D10/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C11&gt;$B$5),"",D11/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C11&gt;$B$5),"",D11/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C12&gt;$B$5),"",D12/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C12&gt;$B$5),"",D12/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C13&gt;$B$5),"",D13/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C13&gt;$B$5),"",D13/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
         <v/>
       </c>
       <c r="H14" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C14&gt;$B$5),"",D14/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C14&gt;$B$5),"",D14/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C15&gt;$B$5),"",D15/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C15&gt;$B$5),"",D15/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C16&gt;$B$5),"",D16/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C16&gt;$B$5),"",D16/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C17&gt;$B$5),"",D17/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C17&gt;$B$5),"",D17/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
         <v/>
       </c>
       <c r="H18" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C18&gt;$B$5),"",D18/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C18&gt;$B$5),"",D18/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C19&gt;$B$5),"",D19/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C19&gt;$B$5),"",D19/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C20&gt;$B$5),"",D20/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C20&gt;$B$5),"",D20/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
         <v/>
       </c>
       <c r="H21" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C21&gt;$B$5),"",D21/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C21&gt;$B$5),"",D21/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>IF(OR(Parametres!$C$96&lt;=0,C22&gt;$B$5),"",D22/Parametres!$C$96)</f>
+        <f>IF(OR(Parametres!$C$64&lt;=0,C22&gt;$B$5),"",D22/Parametres!$C$64)</f>
         <v/>
       </c>
     </row>
